--- a/franquias/pwr_reports/Keys Summary - Franquias (Stores)(2026-09-01 - 2026-09-06) acumulado.xlsx
+++ b/franquias/pwr_reports/Keys Summary - Franquias (Stores)(2026-09-01 - 2026-09-06) acumulado.xlsx
@@ -855,45 +855,45 @@
 146</t>
   </si>
   <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>R$ 5.948.105,99</t>
-  </si>
-  <si>
-    <t>R$ 38.374,88
-R$ 39.312,69</t>
+    <t>135</t>
+  </si>
+  <si>
+    <t>R$ 6.219.579,44</t>
+  </si>
+  <si>
+    <t>R$ 40.126,32
+R$ 41.057,82</t>
   </si>
   <si>
     <t>(3.8%)
 (1.5%)</t>
   </si>
   <si>
-    <t>408.9</t>
-  </si>
-  <si>
-    <t>(9.4%)</t>
-  </si>
-  <si>
-    <t>58.4%</t>
-  </si>
-  <si>
-    <t>17.2%</t>
-  </si>
-  <si>
-    <t>2.9%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>30.7</t>
-  </si>
-  <si>
-    <t>60.9%</t>
-  </si>
-  <si>
-    <t>18.2%</t>
+    <t>427.5</t>
+  </si>
+  <si>
+    <t>(9.5%)</t>
+  </si>
+  <si>
+    <t>54.6%</t>
+  </si>
+  <si>
+    <t>12.4%</t>
+  </si>
+  <si>
+    <t>3.0%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>30.8</t>
+  </si>
+  <si>
+    <t>60.8%</t>
+  </si>
+  <si>
+    <t>18.3%</t>
   </si>
   <si>
     <t>6.3</t>
@@ -902,16 +902,16 @@
     <t>8.9</t>
   </si>
   <si>
-    <t>14.7</t>
+    <t>15.4</t>
   </si>
   <si>
     <t>22.0</t>
   </si>
   <si>
-    <t>58.7%</t>
-  </si>
-  <si>
-    <t>-R$ 218.775,81</t>
+    <t>58.5%</t>
+  </si>
+  <si>
+    <t>-R$ 227.893,07</t>
   </si>
   <si>
     <t>2.78</t>
@@ -1603,7 +1603,7 @@
         <v>10.06870207373272</v>
       </c>
       <c r="AC2" s="8">
-        <v>18.596793999999999</v>
+        <v>19.321204000000002</v>
       </c>
       <c r="AD2" s="8">
         <v>24.64817374429224</v>
@@ -1732,7 +1732,7 @@
         <v>5.1361372400756142</v>
       </c>
       <c r="AC3" s="8">
-        <v>9.3211080000000006</v>
+        <v>9.9792210000000008</v>
       </c>
       <c r="AD3" s="8">
         <v>15.80158859813084</v>
@@ -1863,7 +1863,7 @@
         <v>8.4286237048665615</v>
       </c>
       <c r="AC4" s="8">
-        <v>12.651532</v>
+        <v>12.283225</v>
       </c>
       <c r="AD4" s="8">
         <v>18.677222424242423</v>
@@ -1994,7 +1994,7 @@
         <v>15.117064285714285</v>
       </c>
       <c r="AC5" s="8">
-        <v>21.361481000000001</v>
+        <v>21.222918</v>
       </c>
       <c r="AD5" s="8">
         <v>27.6234126984127</v>
@@ -2256,7 +2256,7 @@
         <v>8.6694235741444867</v>
       </c>
       <c r="AC7" s="8">
-        <v>14.636365</v>
+        <v>15.481171</v>
       </c>
       <c r="AD7" s="8">
         <v>22.286855471698114</v>
@@ -2387,7 +2387,7 @@
         <v>11.187222083333333</v>
       </c>
       <c r="AC8" s="8">
-        <v>15.925818</v>
+        <v>16.764887000000002</v>
       </c>
       <c r="AD8" s="8">
         <v>23.400816734693876</v>
@@ -2518,7 +2518,7 @@
         <v>4.8383220735785955</v>
       </c>
       <c r="AC9" s="8">
-        <v>16.242335000000001</v>
+        <v>17.093489000000002</v>
       </c>
       <c r="AD9" s="8">
         <v>23.887554769736841</v>
@@ -2649,7 +2649,7 @@
         <v>7.6036291754756871</v>
       </c>
       <c r="AC10" s="8">
-        <v>15.039206999999999</v>
+        <v>14.551397</v>
       </c>
       <c r="AD10" s="8">
         <v>21.400698742138363</v>
@@ -2780,7 +2780,7 @@
         <v>6.9241806954436456</v>
       </c>
       <c r="AC11" s="8">
-        <v>20.949694000000001</v>
+        <v>20.937846</v>
       </c>
       <c r="AD11" s="8">
         <v>27.712930011862397</v>
@@ -3040,7 +3040,7 @@
         <v>8.4676020408163275</v>
       </c>
       <c r="AC13" s="8">
-        <v>14.610739000000001</v>
+        <v>14.982495999999999</v>
       </c>
       <c r="AD13" s="8">
         <v>21.835532994923859</v>
@@ -3171,7 +3171,7 @@
         <v>9.6224003565062386</v>
       </c>
       <c r="AC14" s="8">
-        <v>14.5219</v>
+        <v>13.460870999999999</v>
       </c>
       <c r="AD14" s="8">
         <v>18.36027085987261</v>
@@ -3302,7 +3302,7 @@
         <v>6.4838260355029584</v>
       </c>
       <c r="AC15" s="8">
-        <v>10.739896999999999</v>
+        <v>9.6585509999999992</v>
       </c>
       <c r="AD15" s="8">
         <v>16.917314444444443</v>
@@ -3354,7 +3354,7 @@
         <v>19546</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C16" s="4">
         <v>44</v>
@@ -3391,59 +3391,59 @@
         <v>52</v>
       </c>
       <c r="O16" s="5">
-        <v>36729.520000000004</v>
+        <v>42513.350000000006</v>
       </c>
       <c r="P16" s="5">
-        <v>36729.520000000004</v>
+        <v>42513.350000000006</v>
       </c>
       <c r="Q16" s="6">
-        <v>0.10883109622050613</v>
+        <v>-0.041497562899161289</v>
       </c>
       <c r="R16" s="7">
-        <v>384</v>
+        <v>451</v>
       </c>
       <c r="S16" s="6">
-        <v>0.040650406504065151</v>
+        <v>-0.054507337526205402</v>
       </c>
       <c r="T16" s="6">
-        <v>0.00067735434604100468</v>
+        <v>0.00068626443223128734</v>
       </c>
       <c r="U16" s="6">
-        <v>-0.31858818465365191</v>
+        <v>-0.3162995764859744</v>
       </c>
       <c r="V16" s="6">
-        <v>0.056828730677667451</v>
+        <v>0.059155676981465823</v>
       </c>
       <c r="W16" s="6">
-        <v>0.048853129580784076</v>
+        <v>0.05098012741879903</v>
       </c>
       <c r="X16" s="8">
-        <v>28.447766494845357</v>
+        <v>27.87431471861472</v>
       </c>
       <c r="Y16" s="6">
-        <v>0.53846153846153844</v>
+        <v>0.52155172413793105</v>
       </c>
       <c r="Z16" s="6">
-        <v>0.092783505154639179</v>
+        <v>0.086580086580086577</v>
       </c>
       <c r="AA16" s="8">
-        <v>3.2341643044619421</v>
+        <v>3.1457216517857143</v>
       </c>
       <c r="AB16" s="8">
-        <v>10.230326804123711</v>
+        <v>9.8715221739130428</v>
       </c>
       <c r="AC16" s="8">
-        <v>13.48631</v>
+        <v>13.470632</v>
       </c>
       <c r="AD16" s="8">
-        <v>20.419931443298967</v>
+        <v>19.9535354978355</v>
       </c>
       <c r="AE16" s="6">
-        <v>0.58762886597938147</v>
+        <v>0.61038961038961037</v>
       </c>
       <c r="AF16" s="9"/>
       <c r="AG16" s="5">
-        <v>-5813.3999999999996</v>
+        <v>-6979.1400000000003</v>
       </c>
       <c r="AH16" s="10">
         <v>2</v>
@@ -3485,7 +3485,7 @@
         <v>19547</v>
       </c>
       <c r="B17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C17" s="4">
         <v>44</v>
@@ -3522,55 +3522,55 @@
         <v>52</v>
       </c>
       <c r="O17" s="5">
-        <v>28554.010000000002</v>
+        <v>34644.370000000003</v>
       </c>
       <c r="P17" s="5">
-        <v>28554.010000000002</v>
+        <v>34644.370000000003</v>
       </c>
       <c r="Q17" s="6">
-        <v>-0.050180673175979296</v>
+        <v>-0.11762572438400143</v>
       </c>
       <c r="R17" s="7">
-        <v>313</v>
+        <v>380</v>
       </c>
       <c r="S17" s="6">
-        <v>-0.18701298701298696</v>
+        <v>-0.24453280318091453</v>
       </c>
       <c r="T17" s="6">
-        <v>0.35440906548677403</v>
+        <v>0.29210518188092316</v>
       </c>
       <c r="U17" s="6">
-        <v>-3.6498281677424642</v>
+        <v>-3.6937121385090852</v>
       </c>
       <c r="V17" s="6">
-        <v>0.029395923724898885</v>
+        <v>0.029708463453080543</v>
       </c>
       <c r="W17" s="6">
-        <v>0.005536227661193647</v>
+        <v>0.0062013250637838122</v>
       </c>
       <c r="X17" s="8">
-        <v>37.34970760233918</v>
+        <v>35.888207547169813</v>
       </c>
       <c r="Y17" s="6">
-        <v>0.32748538011695905</v>
+        <v>0.30660377358490565</v>
       </c>
       <c r="Z17" s="6">
-        <v>0.36842105263157893</v>
+        <v>0.32075471698113206</v>
       </c>
       <c r="AA17" s="8">
-        <v>9.7662446202531648</v>
+        <v>9.2736794805194798</v>
       </c>
       <c r="AB17" s="8">
-        <v>10.26343393939394</v>
+        <v>9.6316339805825244</v>
       </c>
       <c r="AC17" s="8">
-        <v>20.948739</v>
+        <v>20.344151</v>
       </c>
       <c r="AD17" s="8">
-        <v>27.730701754385965</v>
+        <v>26.736949528301885</v>
       </c>
       <c r="AE17" s="6">
-        <v>0.32163742690058478</v>
+        <v>0.37735849056603776</v>
       </c>
       <c r="AF17" s="9"/>
       <c r="AG17" s="5">
@@ -3691,7 +3691,7 @@
         <v>12.175653921568628</v>
       </c>
       <c r="AC18" s="8">
-        <v>9.0683969999999992</v>
+        <v>16.255587999999999</v>
       </c>
       <c r="AD18" s="8">
         <v>23.053397087378638</v>
@@ -3824,7 +3824,7 @@
         <v>4.8836530351437695</v>
       </c>
       <c r="AC19" s="8">
-        <v>9.4992239999999999</v>
+        <v>11.369123</v>
       </c>
       <c r="AD19" s="8">
         <v>18.692587462686568</v>
@@ -3955,7 +3955,7 @@
         <v>6.6110434650455927</v>
       </c>
       <c r="AC20" s="8">
-        <v>9.7135259999999999</v>
+        <v>9.5016940000000005</v>
       </c>
       <c r="AD20" s="8">
         <v>15.443131363636365</v>
@@ -4007,7 +4007,7 @@
         <v>19553</v>
       </c>
       <c r="B21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C21" s="4">
         <v>44</v>
@@ -4042,55 +4042,55 @@
         <v>52</v>
       </c>
       <c r="O21" s="5">
-        <v>38185.919999999998</v>
+        <v>51037.239999999998</v>
       </c>
       <c r="P21" s="5">
-        <v>38185.919999999998</v>
+        <v>51037.239999999998</v>
       </c>
       <c r="Q21" s="6">
-        <v>0.13330806687558483</v>
+        <v>0.151171364417092</v>
       </c>
       <c r="R21" s="7">
-        <v>347</v>
+        <v>471</v>
       </c>
       <c r="S21" s="6">
-        <v>0.029673590504450953</v>
+        <v>0.056053811659192876</v>
       </c>
       <c r="T21" s="6">
-        <v>0.31498857432268235</v>
+        <v>0.29382889239308396</v>
       </c>
       <c r="U21" s="6">
-        <v>-0.037997028747768807</v>
+        <v>-0.058258524559713656</v>
       </c>
       <c r="V21" s="6">
-        <v>0.025464857203911808</v>
+        <v>0.022247960508836293</v>
       </c>
       <c r="W21" s="6">
-        <v>-0.0020976579849326664</v>
+        <v>-0.0025960553509554985</v>
       </c>
       <c r="X21" s="8">
-        <v>33.936180416666666</v>
+        <v>32.164185436893206</v>
       </c>
       <c r="Y21" s="6">
-        <v>0.7583333333333333</v>
+        <v>0.74110032362459544</v>
       </c>
       <c r="Z21" s="6">
-        <v>0.14166666666666666</v>
+        <v>0.11003236245954692</v>
       </c>
       <c r="AA21" s="8">
-        <v>8.2924793871866296</v>
+        <v>6.8723830578512395</v>
       </c>
       <c r="AB21" s="8">
-        <v>10.345168067226892</v>
+        <v>9.771162171052632</v>
       </c>
       <c r="AC21" s="8">
         <v>18.623356999999999</v>
       </c>
       <c r="AD21" s="8">
-        <v>25.321042083333335</v>
+        <v>23.469310032362461</v>
       </c>
       <c r="AE21" s="6">
-        <v>0.67500000000000004</v>
+        <v>0.69579288025889963</v>
       </c>
       <c r="AF21" s="9"/>
       <c r="AG21" s="5">
@@ -4215,7 +4215,7 @@
         <v>12.670241640378549</v>
       </c>
       <c r="AC22" s="8">
-        <v>18.658332999999999</v>
+        <v>18.270544000000001</v>
       </c>
       <c r="AD22" s="8">
         <v>24.808769538461537</v>
@@ -4346,7 +4346,7 @@
         <v>4.9157360406091373</v>
       </c>
       <c r="AC23" s="8">
-        <v>9.2704710000000006</v>
+        <v>8.4291660000000004</v>
       </c>
       <c r="AD23" s="8">
         <v>16.095203414634145</v>
@@ -4398,7 +4398,7 @@
         <v>19565</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4435,55 +4435,55 @@
         <v>52</v>
       </c>
       <c r="O24" s="5">
-        <v>36825.940000000002</v>
+        <v>49224.850000000006</v>
       </c>
       <c r="P24" s="5">
-        <v>36825.940000000002</v>
+        <v>49224.850000000006</v>
       </c>
       <c r="Q24" s="6">
-        <v>0.012121790116721654</v>
+        <v>-0.01786503459180655</v>
       </c>
       <c r="R24" s="7">
-        <v>415</v>
+        <v>555</v>
       </c>
       <c r="S24" s="6">
-        <v>-0.12631578947368416</v>
+        <v>-0.13819875776397517</v>
       </c>
       <c r="T24" s="6">
-        <v>0.28782412886134062</v>
+        <v>0.2822249798628132</v>
       </c>
       <c r="U24" s="6">
-        <v>-0.036002771416018167</v>
+        <v>-0.037840799921178024</v>
       </c>
       <c r="V24" s="6">
-        <v>0.093289811475280732</v>
+        <v>0.079274969857703978</v>
       </c>
       <c r="W24" s="6">
-        <v>0.060513730267306137</v>
+        <v>0.050164469774920589</v>
       </c>
       <c r="X24" s="8">
-        <v>23.523858921161825</v>
+        <v>23.392078086419755</v>
       </c>
       <c r="Y24" s="6">
-        <v>0.99170124481327804</v>
+        <v>0.98765432098765427</v>
       </c>
       <c r="Z24" s="6">
-        <v>0.037344398340248962</v>
+        <v>0.027777777777777776</v>
       </c>
       <c r="AA24" s="8">
-        <v>2.7320131188118815</v>
+        <v>2.7714285714285714</v>
       </c>
       <c r="AB24" s="8">
-        <v>5.9706125603864733</v>
+        <v>5.320023611111111</v>
       </c>
       <c r="AC24" s="8">
-        <v>8.7184600000000003</v>
+        <v>8.7954729999999994</v>
       </c>
       <c r="AD24" s="8">
-        <v>15.283610373443985</v>
+        <v>15.083127777777777</v>
       </c>
       <c r="AE24" s="6">
-        <v>0.81742738589211617</v>
+        <v>0.83950617283950613</v>
       </c>
       <c r="AF24" s="9"/>
       <c r="AG24" s="5">
@@ -4608,7 +4608,7 @@
         <v>10.635820643431636</v>
       </c>
       <c r="AC25" s="8">
-        <v>15.234664</v>
+        <v>15.276101000000001</v>
       </c>
       <c r="AD25" s="8">
         <v>21.98045013239188</v>
@@ -4739,7 +4739,7 @@
         <v>10.162339270386266</v>
       </c>
       <c r="AC26" s="8">
-        <v>13.418685</v>
+        <v>13.582421</v>
       </c>
       <c r="AD26" s="8">
         <v>19.066284791666664</v>
@@ -4791,7 +4791,7 @@
         <v>19579</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>44</v>
@@ -4828,59 +4828,59 @@
         <v>52</v>
       </c>
       <c r="O27" s="5">
-        <v>26135.610000000001</v>
+        <v>32573.09</v>
       </c>
       <c r="P27" s="5">
-        <v>26135.610000000001</v>
+        <v>32573.09</v>
       </c>
       <c r="Q27" s="6">
-        <v>-0.27099965691620675</v>
+        <v>-0.24463117519786848</v>
       </c>
       <c r="R27" s="7">
-        <v>313</v>
+        <v>379</v>
       </c>
       <c r="S27" s="6">
-        <v>-0.10826210826210825</v>
+        <v>-0.099762470308788598</v>
       </c>
       <c r="T27" s="6">
-        <v>0.3734256479952065</v>
+        <v>0.33459015708979406</v>
       </c>
       <c r="U27" s="6">
-        <v>0.026751512591441332</v>
+        <v>-0.0032150680208724441</v>
       </c>
       <c r="V27" s="6">
-        <v>0.052027941953526238</v>
+        <v>0.048981137497240826</v>
       </c>
       <c r="W27" s="6">
-        <v>0.0080565175253227306</v>
+        <v>0.008354964174415138</v>
       </c>
       <c r="X27" s="8">
-        <v>32.535673617021281</v>
+        <v>31.790534146341461</v>
       </c>
       <c r="Y27" s="6">
-        <v>0.48728813559322032</v>
+        <v>0.55208333333333337</v>
       </c>
       <c r="Z27" s="6">
-        <v>0.28085106382978725</v>
+        <v>0.22996515679442509</v>
       </c>
       <c r="AA27" s="8">
-        <v>6.3113660550458714</v>
+        <v>6.7704412213740452</v>
       </c>
       <c r="AB27" s="8">
-        <v>11.201892576419214</v>
+        <v>10.104033451957296</v>
       </c>
       <c r="AC27" s="8">
-        <v>13.257277</v>
+        <v>17.779506999999999</v>
       </c>
       <c r="AD27" s="8">
-        <v>24.392056595744684</v>
+        <v>23.953600348432055</v>
       </c>
       <c r="AE27" s="6">
-        <v>0.55744680851063833</v>
+        <v>0.58536585365853655</v>
       </c>
       <c r="AF27" s="9"/>
       <c r="AG27" s="5">
-        <v>-272.19999999999999</v>
+        <v>-284.02999999999997</v>
       </c>
       <c r="AH27" s="10">
         <v>3</v>
@@ -5001,7 +5001,7 @@
         <v>8.2304511278195491</v>
       </c>
       <c r="AC28" s="8">
-        <v>16.770719</v>
+        <v>19.813037000000001</v>
       </c>
       <c r="AD28" s="8">
         <v>25.970325435540069</v>
@@ -5053,7 +5053,7 @@
         <v>19581</v>
       </c>
       <c r="B29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C29" s="4">
         <v>44</v>
@@ -5090,55 +5090,55 @@
         <v>52</v>
       </c>
       <c r="O29" s="5">
-        <v>34691.989999999998</v>
+        <v>52577.989999999998</v>
       </c>
       <c r="P29" s="5">
-        <v>34691.989999999998</v>
+        <v>52577.989999999998</v>
       </c>
       <c r="Q29" s="6">
-        <v>-0.096506056760333303</v>
+        <v>0.046679968650159109</v>
       </c>
       <c r="R29" s="7">
-        <v>339</v>
+        <v>513</v>
       </c>
       <c r="S29" s="6">
-        <v>-0.19668246445497628</v>
+        <v>-0.078994614003590646</v>
       </c>
       <c r="T29" s="6">
-        <v>0.3324992887407151</v>
+        <v>0.32783379699376114</v>
       </c>
       <c r="U29" s="6">
-        <v>0.01673216209274821</v>
+        <v>0.010949108172450107</v>
       </c>
       <c r="V29" s="6">
-        <v>0.046876555654489699</v>
+        <v>0.044787742931975905</v>
       </c>
       <c r="W29" s="6">
-        <v>0.026114990809117611</v>
+        <v>0.026913913978073335</v>
       </c>
       <c r="X29" s="8">
-        <v>45.420661797752807</v>
+        <v>48.240606982543646</v>
       </c>
       <c r="Y29" s="6">
-        <v>0.15241635687732341</v>
+        <v>0.10891089108910891</v>
       </c>
       <c r="Z29" s="6">
-        <v>0.54681647940074907</v>
+        <v>0.62593516209476308</v>
       </c>
       <c r="AA29" s="8">
-        <v>4.1271750733137829</v>
+        <v>7.687662890625</v>
       </c>
       <c r="AB29" s="8">
-        <v>20.423938223938226</v>
+        <v>19.967994858611824</v>
       </c>
       <c r="AC29" s="8">
-        <v>25.159469999999999</v>
+        <v>24.796129000000001</v>
       </c>
       <c r="AD29" s="8">
-        <v>31.867041198501873</v>
+        <v>34.846093017456354</v>
       </c>
       <c r="AE29" s="6">
-        <v>0.2247191011235955</v>
+        <v>0.16957605985037408</v>
       </c>
       <c r="AF29" s="9"/>
       <c r="AG29" s="5">
@@ -5263,7 +5263,7 @@
         <v>4.9895380434782615</v>
       </c>
       <c r="AC30" s="8">
-        <v>10.868141</v>
+        <v>10.175233</v>
       </c>
       <c r="AD30" s="8">
         <v>16.405495675675677</v>
@@ -5315,7 +5315,7 @@
         <v>19596</v>
       </c>
       <c r="B31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C31" s="4">
         <v>44</v>
@@ -5350,57 +5350,57 @@
         <v>52</v>
       </c>
       <c r="O31" s="5">
-        <v>32679.470000000001</v>
+        <v>45471.25</v>
       </c>
       <c r="P31" s="5">
-        <v>32679.470000000001</v>
+        <v>45471.25</v>
       </c>
       <c r="Q31" s="6"/>
       <c r="R31" s="7">
-        <v>375</v>
+        <v>509</v>
       </c>
       <c r="S31" s="6">
-        <v>0.050420168067226934</v>
+        <v>0.045174537987679564</v>
       </c>
       <c r="T31" s="6">
-        <v>0.26707252290199324</v>
+        <v>0.27593693377683703</v>
       </c>
       <c r="U31" s="6">
-        <v>-0.082541164223287583</v>
+        <v>-0.077435141985320394</v>
       </c>
       <c r="V31" s="6">
-        <v>0.056355978233429124</v>
+        <v>0.049989168980399706</v>
       </c>
       <c r="W31" s="6">
-        <v>-0.01292023707850831</v>
+        <v>-0.013112241251340133</v>
       </c>
       <c r="X31" s="8">
-        <v>31.916040375586856</v>
+        <v>33.87613367346939</v>
       </c>
       <c r="Y31" s="6">
-        <v>0.88317757009345799</v>
+        <v>0.90169491525423728</v>
       </c>
       <c r="Z31" s="6">
-        <v>0.18779342723004694</v>
+        <v>0.24829931972789115</v>
       </c>
       <c r="AA31" s="8">
-        <v>5.5458908587257625</v>
+        <v>6.6975183098591549</v>
       </c>
       <c r="AB31" s="8">
-        <v>9.7665876190476197</v>
+        <v>10.087414137931034</v>
       </c>
       <c r="AC31" s="8">
-        <v>18.626559</v>
+        <v>16.769499</v>
       </c>
       <c r="AD31" s="8">
-        <v>23.367448826291078</v>
+        <v>25.373922789115646</v>
       </c>
       <c r="AE31" s="6">
-        <v>0.55868544600938963</v>
+        <v>0.49659863945578231</v>
       </c>
       <c r="AF31" s="9"/>
       <c r="AG31" s="5">
-        <v>1933.54</v>
+        <v>2529.8400000000001</v>
       </c>
       <c r="AH31" s="10">
         <v>3</v>
@@ -5521,7 +5521,7 @@
         <v>5.4744108585858591</v>
       </c>
       <c r="AC32" s="8">
-        <v>10.790404000000001</v>
+        <v>12.512987000000001</v>
       </c>
       <c r="AD32" s="8">
         <v>19.275802222222222</v>
@@ -5650,7 +5650,7 @@
         <v>14.157497264437691</v>
       </c>
       <c r="AC33" s="8">
-        <v>21.155339000000001</v>
+        <v>25.545556000000001</v>
       </c>
       <c r="AD33" s="8">
         <v>32.463030303030301</v>
@@ -5779,7 +5779,7 @@
         <v>8.2126694570135736</v>
       </c>
       <c r="AC34" s="8">
-        <v>11.658073</v>
+        <v>11.88678</v>
       </c>
       <c r="AD34" s="8">
         <v>19.530968514412418</v>
@@ -5831,7 +5831,7 @@
         <v>19601</v>
       </c>
       <c r="B35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C35" s="4">
         <v>44</v>
@@ -5868,59 +5868,59 @@
         <v>52</v>
       </c>
       <c r="O35" s="5">
-        <v>30230.720000000001</v>
+        <v>41249.160000000003</v>
       </c>
       <c r="P35" s="5">
-        <v>30230.720000000001</v>
+        <v>41249.160000000003</v>
       </c>
       <c r="Q35" s="6">
-        <v>-0.12562196357548761</v>
+        <v>-0.17659641743279686</v>
       </c>
       <c r="R35" s="7">
-        <v>351</v>
+        <v>474</v>
       </c>
       <c r="S35" s="6">
-        <v>-0.19310344827586212</v>
+        <v>-0.23548387096774193</v>
       </c>
       <c r="T35" s="6">
-        <v>0.33436600914566372</v>
+        <v>0.32282620058202394</v>
       </c>
       <c r="U35" s="6">
-        <v>0.02148659376951657</v>
+        <v>0.0045089306061020388</v>
       </c>
       <c r="V35" s="6">
-        <v>0.068913244540652688</v>
+        <v>0.065964809950069273</v>
       </c>
       <c r="W35" s="6">
-        <v>0.029277403912311713</v>
+        <v>0.030683849077169083</v>
       </c>
       <c r="X35" s="8">
-        <v>23.043198654708522</v>
+        <v>22.713087248322147</v>
       </c>
       <c r="Y35" s="6">
-        <v>0.9282511210762332</v>
+        <v>0.93288590604026844</v>
       </c>
       <c r="Z35" s="6">
-        <v>0.017937219730941704</v>
+        <v>0.013422818791946308</v>
       </c>
       <c r="AA35" s="8">
-        <v>2.7497008982035926</v>
+        <v>2.936337142857143</v>
       </c>
       <c r="AB35" s="8">
-        <v>5.5355304545454551</v>
+        <v>5.5166093103448279</v>
       </c>
       <c r="AC35" s="8">
-        <v>8.6598419999999994</v>
+        <v>8.3782160000000001</v>
       </c>
       <c r="AD35" s="8">
-        <v>16.137369506726458</v>
+        <v>16.133389597315436</v>
       </c>
       <c r="AE35" s="6">
-        <v>0.8699551569506726</v>
+        <v>0.8825503355704698</v>
       </c>
       <c r="AF35" s="9"/>
       <c r="AG35" s="5">
-        <v>-11.83</v>
+        <v>-65.230000000000004</v>
       </c>
       <c r="AH35" s="10">
         <v>4</v>
@@ -6136,7 +6136,7 @@
         <v>11.507209302325583</v>
       </c>
       <c r="AC37" s="8">
-        <v>7.9965070000000003</v>
+        <v>19.508388</v>
       </c>
       <c r="AD37" s="8">
         <v>26.88946143497758</v>
@@ -6265,7 +6265,7 @@
         <v>2.86252009569378</v>
       </c>
       <c r="AC38" s="8">
-        <v>6.0597390000000004</v>
+        <v>5.8196960000000004</v>
       </c>
       <c r="AD38" s="8">
         <v>12.75637942583732</v>
@@ -6317,7 +6317,7 @@
         <v>19609</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -6354,59 +6354,59 @@
         <v>52</v>
       </c>
       <c r="O39" s="5">
-        <v>28181.110000000001</v>
+        <v>37043.520000000004</v>
       </c>
       <c r="P39" s="5">
-        <v>28181.110000000001</v>
+        <v>37043.520000000004</v>
       </c>
       <c r="Q39" s="6">
-        <v>-0.047796824470049626</v>
+        <v>-0.034525969669690126</v>
       </c>
       <c r="R39" s="7">
-        <v>300</v>
+        <v>398</v>
       </c>
       <c r="S39" s="6">
-        <v>-0.16434540389972141</v>
+        <v>-0.15138592750533053</v>
       </c>
       <c r="T39" s="6">
-        <v>0.32427563712004243</v>
+        <v>0.32694504463938634</v>
       </c>
       <c r="U39" s="6">
-        <v>-0.042400125474120781</v>
+        <v>-0.03886657369494044</v>
       </c>
       <c r="V39" s="6">
-        <v>0.016714920029764619</v>
+        <v>0.015702300969238345</v>
       </c>
       <c r="W39" s="6">
-        <v>-0.0088997559003176248</v>
+        <v>-0.007888599679512099</v>
       </c>
       <c r="X39" s="8">
-        <v>40.716869512195117</v>
+        <v>39.518055128205127</v>
       </c>
       <c r="Y39" s="6">
-        <v>0.32520325203252032</v>
+        <v>0.33974358974358976</v>
       </c>
       <c r="Z39" s="6">
-        <v>0.44308943089430897</v>
+        <v>0.41346153846153844</v>
       </c>
       <c r="AA39" s="8">
-        <v>5.934539802631579</v>
+        <v>5.792103241895262</v>
       </c>
       <c r="AB39" s="8">
-        <v>16.024490204081633</v>
+        <v>15.147856591639872</v>
       </c>
       <c r="AC39" s="8">
-        <v>20.067112999999999</v>
+        <v>22.261704000000002</v>
       </c>
       <c r="AD39" s="8">
-        <v>29.053455284552843</v>
+        <v>28.093322756410259</v>
       </c>
       <c r="AE39" s="6">
-        <v>0.26422764227642276</v>
+        <v>0.27564102564102566</v>
       </c>
       <c r="AF39" s="9"/>
       <c r="AG39" s="5">
-        <v>-594.34000000000003</v>
+        <v>-702.13999999999999</v>
       </c>
       <c r="AH39" s="10">
         <v>2</v>
@@ -6527,7 +6527,7 @@
         <v>9.2487229838709677</v>
       </c>
       <c r="AC40" s="8">
-        <v>13.956787</v>
+        <v>12.65774</v>
       </c>
       <c r="AD40" s="8">
         <v>19.359156521739131</v>
@@ -6656,7 +6656,7 @@
         <v>6.9386894139886577</v>
       </c>
       <c r="AC41" s="8">
-        <v>12.771393</v>
+        <v>14.428429</v>
       </c>
       <c r="AD41" s="8">
         <v>22.621094464944651</v>
@@ -6787,7 +6787,7 @@
         <v>7.1093396284829717</v>
       </c>
       <c r="AC42" s="8">
-        <v>13.387677999999999</v>
+        <v>12.950559</v>
       </c>
       <c r="AD42" s="8">
         <v>19.57891536144578</v>
@@ -6934,7 +6934,7 @@
         <v>19622</v>
       </c>
       <c r="B44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C44" s="4">
         <v>44</v>
@@ -6971,59 +6971,59 @@
         <v>52</v>
       </c>
       <c r="O44" s="5">
-        <v>30104.360000000001</v>
+        <v>37353.410000000003</v>
       </c>
       <c r="P44" s="5">
-        <v>30104.360000000001</v>
+        <v>37353.410000000003</v>
       </c>
       <c r="Q44" s="6">
-        <v>0.53577218767376977</v>
+        <v>0.26581994939893461</v>
       </c>
       <c r="R44" s="7">
-        <v>338</v>
+        <v>429</v>
       </c>
       <c r="S44" s="6">
-        <v>0.45064377682403434</v>
+        <v>0.2152974504249292</v>
       </c>
       <c r="T44" s="6">
-        <v>0.26481120342701192</v>
+        <v>0.28264864171704807</v>
       </c>
       <c r="U44" s="6">
-        <v>-0.077824547673493144</v>
+        <v>-0.065131386933615962</v>
       </c>
       <c r="V44" s="6">
-        <v>0.040019734682949573</v>
+        <v>0.039047720141213341</v>
       </c>
       <c r="W44" s="6">
-        <v>0.018689933949766743</v>
+        <v>0.018958523465461383</v>
       </c>
       <c r="X44" s="8">
-        <v>24.653666000000001</v>
+        <v>24.589891612903227</v>
       </c>
       <c r="Y44" s="6">
-        <v>0.8666666666666667</v>
+        <v>0.87096774193548387</v>
       </c>
       <c r="Z44" s="6">
         <v>0</v>
       </c>
       <c r="AA44" s="8">
-        <v>4.8437756172839501</v>
+        <v>4.4859756097560979</v>
       </c>
       <c r="AB44" s="8">
-        <v>3.0117021276595741</v>
+        <v>3.0248856164383562</v>
       </c>
       <c r="AC44" s="8">
         <v>8.1929379999999998</v>
       </c>
       <c r="AD44" s="8">
-        <v>14.665333333333335</v>
+        <v>14.624730967741934</v>
       </c>
       <c r="AE44" s="6">
-        <v>0.87333333333333329</v>
+        <v>0.8774193548387097</v>
       </c>
       <c r="AF44" s="9"/>
       <c r="AG44" s="5">
-        <v>-672.70000000000005</v>
+        <v>-1013.1</v>
       </c>
       <c r="AH44" s="10">
         <v>1</v>
@@ -7144,7 +7144,7 @@
         <v>6.1085739884393071</v>
       </c>
       <c r="AC45" s="8">
-        <v>11.385685</v>
+        <v>11.277972</v>
       </c>
       <c r="AD45" s="8">
         <v>18.779281767955801</v>
@@ -7273,7 +7273,7 @@
         <v>5.0379406504065036</v>
       </c>
       <c r="AC46" s="8">
-        <v>8.3497570000000003</v>
+        <v>7.9710200000000002</v>
       </c>
       <c r="AD46" s="8">
         <v>14.343812878787878</v>
@@ -7402,7 +7402,7 @@
         <v>5.7341162393162399</v>
       </c>
       <c r="AC47" s="8">
-        <v>9.5702660000000002</v>
+        <v>9.7378049999999998</v>
       </c>
       <c r="AD47" s="8">
         <v>16.054065040650407</v>
@@ -7533,7 +7533,7 @@
         <v>11.961219553072626</v>
       </c>
       <c r="AC48" s="8">
-        <v>14.957217</v>
+        <v>16.953557</v>
       </c>
       <c r="AD48" s="8">
         <v>22.343018108108108</v>
@@ -7662,7 +7662,7 @@
         <v>7.0640172185430465</v>
       </c>
       <c r="AC49" s="8">
-        <v>12.809215999999999</v>
+        <v>13.909772</v>
       </c>
       <c r="AD49" s="8">
         <v>20.570170063694267</v>
@@ -7886,7 +7886,7 @@
         <v>14.741138732394367</v>
       </c>
       <c r="AC51" s="8">
-        <v>23.596606999999999</v>
+        <v>21.800758999999999</v>
       </c>
       <c r="AD51" s="8">
         <v>28.344059861591695</v>
@@ -8146,7 +8146,7 @@
         <v>13.873839556962027</v>
       </c>
       <c r="AC53" s="8">
-        <v>18.493009000000001</v>
+        <v>19.761763999999999</v>
       </c>
       <c r="AD53" s="8">
         <v>27.687077848101264</v>
@@ -8277,7 +8277,7 @@
         <v>9.9360153256704979</v>
       </c>
       <c r="AC54" s="8">
-        <v>17.073278999999999</v>
+        <v>20.267240999999999</v>
       </c>
       <c r="AD54" s="8">
         <v>27.20989808429119</v>
@@ -8329,7 +8329,7 @@
         <v>19649</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -8364,59 +8364,59 @@
         <v>52</v>
       </c>
       <c r="O55" s="5">
-        <v>35821.169999999998</v>
+        <v>48331.459999999999</v>
       </c>
       <c r="P55" s="5">
-        <v>35821.169999999998</v>
+        <v>48331.459999999999</v>
       </c>
       <c r="Q55" s="6">
-        <v>-0.043262001434793196</v>
+        <v>-0.090653449147181875</v>
       </c>
       <c r="R55" s="7">
-        <v>422</v>
+        <v>564</v>
       </c>
       <c r="S55" s="6">
-        <v>-0.11344537815126055</v>
+        <v>-0.14803625377643503</v>
       </c>
       <c r="T55" s="6">
-        <v>0.27191956320801358</v>
+        <v>0.267550760932941</v>
       </c>
       <c r="U55" s="6">
-        <v>-0.046253461291186196</v>
+        <v>-0.047862636469082454</v>
       </c>
       <c r="V55" s="6">
-        <v>0.047622746549037899</v>
+        <v>0.044785446166947983</v>
       </c>
       <c r="W55" s="6">
-        <v>0.0077932267427334185</v>
+        <v>0.008102507145449361</v>
       </c>
       <c r="X55" s="8">
-        <v>23.692797487437183</v>
+        <v>23.710103088803088</v>
       </c>
       <c r="Y55" s="6">
-        <v>0.97989949748743721</v>
+        <v>0.97683397683397688</v>
       </c>
       <c r="Z55" s="6">
-        <v>0.040201005025125629</v>
+        <v>0.034749034749034749</v>
       </c>
       <c r="AA55" s="8">
-        <v>2.7909351219512195</v>
+        <v>2.9328806159420289</v>
       </c>
       <c r="AB55" s="8">
-        <v>5.6111400000000007</v>
+        <v>5.2705125506072878</v>
       </c>
       <c r="AC55" s="8">
-        <v>7.9959959999999999</v>
+        <v>8.3626690000000004</v>
       </c>
       <c r="AD55" s="8">
-        <v>15.79673417085427</v>
+        <v>15.573810038610038</v>
       </c>
       <c r="AE55" s="6">
-        <v>0.82914572864321612</v>
+        <v>0.84169884169884168</v>
       </c>
       <c r="AF55" s="9"/>
       <c r="AG55" s="5">
-        <v>-774.70000000000005</v>
+        <v>-870</v>
       </c>
       <c r="AH55" s="10">
         <v>5</v>
@@ -8535,7 +8535,7 @@
         <v>6.6300441636582432</v>
       </c>
       <c r="AC56" s="8">
-        <v>15.575569</v>
+        <v>14.95622</v>
       </c>
       <c r="AD56" s="8">
         <v>21.843205395683452</v>
@@ -8664,7 +8664,7 @@
         <v>4.3079216049382714</v>
       </c>
       <c r="AC57" s="8">
-        <v>7.5608139999999997</v>
+        <v>7.3999319999999997</v>
       </c>
       <c r="AD57" s="8">
         <v>15.081449404761905</v>
@@ -8807,7 +8807,7 @@
         <v>19657</v>
       </c>
       <c r="B59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C59" s="4">
         <v>44</v>
@@ -8844,59 +8844,59 @@
         <v>52</v>
       </c>
       <c r="O59" s="5">
-        <v>29022.25</v>
+        <v>40031.699999999997</v>
       </c>
       <c r="P59" s="5">
-        <v>29022.25</v>
+        <v>40031.699999999997</v>
       </c>
       <c r="Q59" s="6">
-        <v>0.29705713312709547</v>
+        <v>0.39245635845167359</v>
       </c>
       <c r="R59" s="7">
-        <v>291</v>
+        <v>403</v>
       </c>
       <c r="S59" s="6">
-        <v>0.13229571984435795</v>
+        <v>0.21021021021021014</v>
       </c>
       <c r="T59" s="6">
         <v>0</v>
       </c>
       <c r="U59" s="6">
-        <v>-0.31572638234458045</v>
+        <v>-0.30709312869550881</v>
       </c>
       <c r="V59" s="6">
-        <v>0.045839485222544774</v>
+        <v>0.040903858691986601</v>
       </c>
       <c r="W59" s="6">
-        <v>0.024406619059514682</v>
+        <v>0.021866445841670478</v>
       </c>
       <c r="X59" s="8">
-        <v>34.516298342541432</v>
+        <v>36.165840082644628</v>
       </c>
       <c r="Y59" s="6">
-        <v>0.49171270718232046</v>
+        <v>0.4567901234567901</v>
       </c>
       <c r="Z59" s="6">
-        <v>0.24861878453038674</v>
+        <v>0.29338842975206614</v>
       </c>
       <c r="AA59" s="8">
-        <v>9.5109965635738831</v>
+        <v>9.7089359102244384</v>
       </c>
       <c r="AB59" s="8">
-        <v>11.808938547486035</v>
+        <v>13.040871369294605</v>
       </c>
       <c r="AC59" s="8">
-        <v>22.272967000000001</v>
+        <v>21.435676999999998</v>
       </c>
       <c r="AD59" s="8">
-        <v>28.097606077348065</v>
+        <v>29.423113991769547</v>
       </c>
       <c r="AE59" s="6">
-        <v>0.43093922651933703</v>
+        <v>0.41735537190082644</v>
       </c>
       <c r="AF59" s="9"/>
       <c r="AG59" s="5">
-        <v>-1795.22</v>
+        <v>-2334.02</v>
       </c>
       <c r="AH59" s="10">
         <v>3</v>
@@ -9239,7 +9239,7 @@
         <v>16.416448196721312</v>
       </c>
       <c r="AC62" s="8">
-        <v>23.739132000000001</v>
+        <v>24.120114999999998</v>
       </c>
       <c r="AD62" s="8">
         <v>30.952388925081436</v>
@@ -9291,7 +9291,7 @@
         <v>19674</v>
       </c>
       <c r="B63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C63" s="4">
         <v>44</v>
@@ -9326,59 +9326,59 @@
         <v>52</v>
       </c>
       <c r="O63" s="5">
-        <v>33488.919999999998</v>
+        <v>38163.599999999999</v>
       </c>
       <c r="P63" s="5">
-        <v>33488.919999999998</v>
+        <v>38163.599999999999</v>
       </c>
       <c r="Q63" s="6">
-        <v>-0.17168572708378238</v>
+        <v>-0.20617081567614848</v>
       </c>
       <c r="R63" s="7">
-        <v>385</v>
+        <v>440</v>
       </c>
       <c r="S63" s="6">
-        <v>-0.12698412698412698</v>
+        <v>-0.16190476190476188</v>
       </c>
       <c r="T63" s="6">
-        <v>0.056240410261065452</v>
+        <v>0.18456256223207454</v>
       </c>
       <c r="U63" s="6">
-        <v>-0.37297020626523641</v>
+        <v>-0.24365385341005563</v>
       </c>
       <c r="V63" s="6">
-        <v>0.02956712249902356</v>
+        <v>0.030566966952803195</v>
       </c>
       <c r="W63" s="6">
-        <v>-0.0012711368416777849</v>
+        <v>-0.0015062651322202308</v>
       </c>
       <c r="X63" s="8">
-        <v>29.374966122448978</v>
+        <v>28.945087719298247</v>
       </c>
       <c r="Y63" s="6">
-        <v>0.70612244897959187</v>
+        <v>0.68421052631578949</v>
       </c>
       <c r="Z63" s="6">
-        <v>0.11428571428571428</v>
+        <v>0.11228070175438597</v>
       </c>
       <c r="AA63" s="8">
-        <v>5.5033678756476689</v>
+        <v>5.3882801369863014</v>
       </c>
       <c r="AB63" s="8">
-        <v>6.1525038626609447</v>
+        <v>6.1687190298507462</v>
       </c>
       <c r="AC63" s="8">
         <v>11.740339000000001</v>
       </c>
       <c r="AD63" s="8">
-        <v>21.228299591836734</v>
+        <v>21.027368771929826</v>
       </c>
       <c r="AE63" s="6">
-        <v>0.62857142857142856</v>
+        <v>0.63859649122807016</v>
       </c>
       <c r="AF63" s="9"/>
       <c r="AG63" s="5">
-        <v>-303.69999999999999</v>
+        <v>-355.60000000000002</v>
       </c>
       <c r="AH63" s="10">
         <v>3</v>
@@ -9501,7 +9501,7 @@
         <v>7.2758527559055119</v>
       </c>
       <c r="AC64" s="8">
-        <v>12.386956</v>
+        <v>12.357388</v>
       </c>
       <c r="AD64" s="8">
         <v>18.959796183206105</v>
@@ -9632,7 +9632,7 @@
         <v>8.5287291291291289</v>
       </c>
       <c r="AC65" s="8">
-        <v>15.715266</v>
+        <v>15.113155000000001</v>
       </c>
       <c r="AD65" s="8">
         <v>21.895858682634731</v>
@@ -9856,7 +9856,7 @@
         <v>11.18198153153153</v>
       </c>
       <c r="AC67" s="8">
-        <v>16.552620000000001</v>
+        <v>20.089426</v>
       </c>
       <c r="AD67" s="8">
         <v>25.816044398340249</v>
@@ -9987,7 +9987,7 @@
         <v>14.825000000000001</v>
       </c>
       <c r="AC68" s="8">
-        <v>19.519739999999999</v>
+        <v>19.873494999999998</v>
       </c>
       <c r="AD68" s="8">
         <v>20.794385263157896</v>
@@ -10118,7 +10118,7 @@
         <v>5.2757914027149324</v>
       </c>
       <c r="AC69" s="8">
-        <v>13.161118</v>
+        <v>16.452729999999999</v>
       </c>
       <c r="AD69" s="8">
         <v>24.597870925110133</v>
@@ -10249,7 +10249,7 @@
         <v>4.8075111111111104</v>
       </c>
       <c r="AC70" s="8">
-        <v>8.9241449999999993</v>
+        <v>8.9019619999999993</v>
       </c>
       <c r="AD70" s="8">
         <v>13.831690610328637</v>
@@ -10378,7 +10378,7 @@
         <v>8.5288716923076926</v>
       </c>
       <c r="AC71" s="8">
-        <v>11.852395</v>
+        <v>12.441636000000001</v>
       </c>
       <c r="AD71" s="8">
         <v>18.701795076923077</v>
@@ -10523,7 +10523,7 @@
         <v>19694</v>
       </c>
       <c r="B73" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C73" s="4">
         <v>44</v>
@@ -10560,59 +10560,59 @@
         <v>52</v>
       </c>
       <c r="O73" s="5">
-        <v>31617.090000000004</v>
+        <v>41442.980000000003</v>
       </c>
       <c r="P73" s="5">
-        <v>31617.090000000004</v>
+        <v>41442.980000000003</v>
       </c>
       <c r="Q73" s="6">
-        <v>0.16733616837771126</v>
+        <v>0.20027305406980322</v>
       </c>
       <c r="R73" s="7">
-        <v>336</v>
+        <v>439</v>
       </c>
       <c r="S73" s="6">
-        <v>0.030674846625766916</v>
+        <v>0.065533980582524354</v>
       </c>
       <c r="T73" s="6">
-        <v>-10.671722954263027</v>
+        <v>-7.5629366734728043</v>
       </c>
       <c r="U73" s="6">
-        <v>-16.38890502256849</v>
+        <v>-13.202675659424102</v>
       </c>
       <c r="V73" s="6">
-        <v>0.082165752762192859</v>
+        <v>0.082291958734627663</v>
       </c>
       <c r="W73" s="6">
-        <v>0.052920177030839968</v>
+        <v>0.054014310746958831</v>
       </c>
       <c r="X73" s="8">
-        <v>46.977657758620687</v>
+        <v>44.326281730769232</v>
       </c>
       <c r="Y73" s="6">
-        <v>0.39240506329113922</v>
+        <v>0.39432176656151419</v>
       </c>
       <c r="Z73" s="6">
-        <v>0.47844827586206895</v>
+        <v>0.43269230769230771</v>
       </c>
       <c r="AA73" s="8">
-        <v>10.901355421686747</v>
+        <v>9.9229885057471261</v>
       </c>
       <c r="AB73" s="8">
-        <v>18.909242794759823</v>
+        <v>17.917045129870129</v>
       </c>
       <c r="AC73" s="8">
-        <v>22.373427</v>
+        <v>30.407142</v>
       </c>
       <c r="AD73" s="8">
-        <v>37.11027327586207</v>
+        <v>34.922062179487178</v>
       </c>
       <c r="AE73" s="6">
-        <v>0.31034482758620691</v>
+        <v>0.32371794871794873</v>
       </c>
       <c r="AF73" s="9"/>
       <c r="AG73" s="5">
-        <v>-2061.7600000000002</v>
+        <v>-2588.1500000000001</v>
       </c>
       <c r="AH73" s="10">
         <v>2</v>
@@ -10733,7 +10733,7 @@
         <v>4.7103387218045114</v>
       </c>
       <c r="AC74" s="8">
-        <v>10.761163</v>
+        <v>10.577731</v>
       </c>
       <c r="AD74" s="8">
         <v>17.212545090909089</v>
@@ -10864,7 +10864,7 @@
         <v>6.0105206249999998</v>
       </c>
       <c r="AC75" s="8">
-        <v>12.058959</v>
+        <v>12.582877</v>
       </c>
       <c r="AD75" s="8">
         <v>20.490416250000003</v>
@@ -10993,7 +10993,7 @@
         <v>5.4561447004608299</v>
       </c>
       <c r="AC76" s="8">
-        <v>8.9359769999999994</v>
+        <v>11.037048</v>
       </c>
       <c r="AD76" s="8">
         <v>18.111854811715482</v>
@@ -11217,7 +11217,7 @@
         <v>10.611027272727274</v>
       </c>
       <c r="AC78" s="8">
-        <v>18.272490999999999</v>
+        <v>19.564112000000002</v>
       </c>
       <c r="AD78" s="8">
         <v>25.250542790697672</v>
@@ -11269,7 +11269,7 @@
         <v>19715</v>
       </c>
       <c r="B79" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C79" s="4">
         <v>44</v>
@@ -11306,59 +11306,59 @@
         <v>52</v>
       </c>
       <c r="O79" s="5">
-        <v>32750.489999999998</v>
+        <v>43123.209999999999</v>
       </c>
       <c r="P79" s="5">
-        <v>32750.489999999998</v>
+        <v>43123.209999999999</v>
       </c>
       <c r="Q79" s="6">
-        <v>0.41055918036324246</v>
+        <v>0.47910169782198597</v>
       </c>
       <c r="R79" s="7">
-        <v>349</v>
+        <v>457</v>
       </c>
       <c r="S79" s="6">
-        <v>0.24642857142857144</v>
+        <v>0.30199430199430188</v>
       </c>
       <c r="T79" s="6">
-        <v>0.92477681707968329</v>
+        <v>0.7023339380347613</v>
       </c>
       <c r="U79" s="6">
-        <v>0.54459563505767394</v>
+        <v>0.33027304553626691</v>
       </c>
       <c r="V79" s="6">
-        <v>0.030349087906776356</v>
+        <v>0.035328422907292843</v>
       </c>
       <c r="W79" s="6">
-        <v>0.0043360419950968666</v>
+        <v>0.011252525032343372</v>
       </c>
       <c r="X79" s="8">
-        <v>34.782579185520362</v>
+        <v>34.591264482758625</v>
       </c>
       <c r="Y79" s="6">
         <v>1</v>
       </c>
       <c r="Z79" s="6">
-        <v>0.26244343891402716</v>
+        <v>0.25862068965517243</v>
       </c>
       <c r="AA79" s="8">
-        <v>11.422174928774929</v>
+        <v>11.209154048140045</v>
       </c>
       <c r="AB79" s="8">
-        <v>10.066666363636363</v>
+        <v>9.9784142361111119</v>
       </c>
       <c r="AC79" s="8">
         <v>21.505828000000001</v>
       </c>
       <c r="AD79" s="8">
-        <v>30.429034841628962</v>
+        <v>30.283678275862069</v>
       </c>
       <c r="AE79" s="6">
-        <v>0.38461538461538464</v>
+        <v>0.3896551724137931</v>
       </c>
       <c r="AF79" s="9"/>
       <c r="AG79" s="5">
-        <v>-795.79999999999995</v>
+        <v>-847.70000000000005</v>
       </c>
       <c r="AH79" s="10">
         <v>3</v>
@@ -11477,7 +11477,7 @@
         <v>16.457471428571427</v>
       </c>
       <c r="AC80" s="8">
-        <v>19.572051999999999</v>
+        <v>22.322431999999999</v>
       </c>
       <c r="AD80" s="8">
         <v>28.134108372093024</v>
@@ -11703,7 +11703,7 @@
         <v>7.5700158878504675</v>
       </c>
       <c r="AC82" s="8">
-        <v>14.303452</v>
+        <v>13.991258</v>
       </c>
       <c r="AD82" s="8">
         <v>18.716597933884298</v>
@@ -11834,7 +11834,7 @@
         <v>5.4387404580152676</v>
       </c>
       <c r="AC83" s="8">
-        <v>15.163677</v>
+        <v>13.699624999999999</v>
       </c>
       <c r="AD83" s="8">
         <v>21.908520149253732</v>
@@ -11963,7 +11963,7 @@
         <v>9.7500888297872343</v>
       </c>
       <c r="AC84" s="8">
-        <v>13.185432</v>
+        <v>13.11364</v>
       </c>
       <c r="AD84" s="8">
         <v>18.839285714285715</v>
@@ -12094,7 +12094,7 @@
         <v>1.0062499999999999</v>
       </c>
       <c r="AC85" s="8">
-        <v>6.472378</v>
+        <v>6.6639939999999998</v>
       </c>
       <c r="AD85" s="8">
         <v>13.708680208333334</v>
@@ -12225,7 +12225,7 @@
         <v>11.940682677165354</v>
       </c>
       <c r="AC86" s="8">
-        <v>19.361419999999999</v>
+        <v>20.482904000000001</v>
       </c>
       <c r="AD86" s="8">
         <v>27.459120472440947</v>
@@ -12370,7 +12370,7 @@
         <v>19730</v>
       </c>
       <c r="B88" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C88" s="4">
         <v>44</v>
@@ -12405,59 +12405,59 @@
         <v>52</v>
       </c>
       <c r="O88" s="5">
-        <v>43526.07</v>
+        <v>56224</v>
       </c>
       <c r="P88" s="5">
-        <v>43526.07</v>
+        <v>56224</v>
       </c>
       <c r="Q88" s="6">
-        <v>0.03624124483975244</v>
+        <v>0.028357567154452479</v>
       </c>
       <c r="R88" s="7">
-        <v>442</v>
+        <v>580</v>
       </c>
       <c r="S88" s="6">
-        <v>-0.028571428571428581</v>
+        <v>-0.039735099337748325</v>
       </c>
       <c r="T88" s="6">
-        <v>-0.00057896336609301045</v>
+        <v>0.26502758430563461</v>
       </c>
       <c r="U88" s="6">
-        <v>-0.34178918519406876</v>
+        <v>-0.072514746371656238</v>
       </c>
       <c r="V88" s="6">
-        <v>0.034184099322543939</v>
+        <v>0.033548280093910074</v>
       </c>
       <c r="W88" s="6">
-        <v>0.016472645014815261</v>
+        <v>0.017875969336937962</v>
       </c>
       <c r="X88" s="8">
-        <v>27.814041732283464</v>
+        <v>27.223964705882352</v>
       </c>
       <c r="Y88" s="6">
-        <v>0.46456692913385828</v>
+        <v>0.5163398692810458</v>
       </c>
       <c r="Z88" s="6">
-        <v>0.13385826771653545</v>
+        <v>0.11764705882352941</v>
       </c>
       <c r="AA88" s="8">
-        <v>4.8321029082774043</v>
+        <v>4.8923623509369678</v>
       </c>
       <c r="AB88" s="8">
-        <v>10.552887401574802</v>
+        <v>10.149564705882353</v>
       </c>
       <c r="AC88" s="8">
         <v>15.777626</v>
       </c>
       <c r="AD88" s="8">
-        <v>23.727558267716535</v>
+        <v>23.244443790849672</v>
       </c>
       <c r="AE88" s="6">
-        <v>0.73228346456692917</v>
+        <v>0.75163398692810457</v>
       </c>
       <c r="AF88" s="9"/>
       <c r="AG88" s="5">
-        <v>-273.94</v>
+        <v>-390.83999999999997</v>
       </c>
       <c r="AH88" s="10">
         <v>2</v>
@@ -12671,7 +12671,7 @@
         <v>1.6161295698924731</v>
       </c>
       <c r="AC90" s="8">
-        <v>7.6226120000000002</v>
+        <v>7.5950290000000003</v>
       </c>
       <c r="AD90" s="8">
         <v>14.508110160427806</v>
@@ -12893,7 +12893,7 @@
         <v>5.0938442508710802</v>
       </c>
       <c r="AC92" s="8">
-        <v>7.3580040000000002</v>
+        <v>12.809341</v>
       </c>
       <c r="AD92" s="8">
         <v>21.267758035714287</v>
@@ -13024,7 +13024,7 @@
         <v>4.5400681506849319</v>
       </c>
       <c r="AC93" s="8">
-        <v>10.355266</v>
+        <v>9.3165700000000005</v>
       </c>
       <c r="AD93" s="8">
         <v>17.113111</v>
@@ -13155,7 +13155,7 @@
         <v>4.3169349462365592</v>
       </c>
       <c r="AC94" s="8">
-        <v>7.4183300000000001</v>
+        <v>8.1034830000000007</v>
       </c>
       <c r="AD94" s="8">
         <v>15.66531269035533</v>
@@ -13284,7 +13284,7 @@
         <v>18.392604929577463</v>
       </c>
       <c r="AC95" s="8">
-        <v>18.855080000000001</v>
+        <v>25.941040000000001</v>
       </c>
       <c r="AD95" s="8">
         <v>32.902252027027025</v>
@@ -13415,7 +13415,7 @@
         <v>11.049999514563106</v>
       </c>
       <c r="AC96" s="8">
-        <v>19.508215</v>
+        <v>21.218326000000001</v>
       </c>
       <c r="AD96" s="8">
         <v>25.385458167330679</v>
@@ -13467,7 +13467,7 @@
         <v>19749</v>
       </c>
       <c r="B97" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C97" s="4">
         <v>44</v>
@@ -13502,59 +13502,59 @@
         <v>52</v>
       </c>
       <c r="O97" s="5">
-        <v>19428.670000000002</v>
+        <v>24519.530000000002</v>
       </c>
       <c r="P97" s="5">
-        <v>19428.670000000002</v>
+        <v>24519.530000000002</v>
       </c>
       <c r="Q97" s="6">
-        <v>-0.17954360414048454</v>
+        <v>-0.14790788610382088</v>
       </c>
       <c r="R97" s="7">
-        <v>199</v>
+        <v>249</v>
       </c>
       <c r="S97" s="6">
-        <v>-0.25187969924812026</v>
+        <v>-0.24316109422492405</v>
       </c>
       <c r="T97" s="6">
-        <v>9.3056704550543099</v>
+        <v>-0.64353943978534667</v>
       </c>
       <c r="U97" s="6">
-        <v>5.5915876073864048</v>
+        <v>-4.3216874303871249</v>
       </c>
       <c r="V97" s="6">
-        <v>0.035029366395126375</v>
+        <v>0.031467752440605505</v>
       </c>
       <c r="W97" s="6">
-        <v>0.023302881772143954</v>
+        <v>0.020089883452089008</v>
       </c>
       <c r="X97" s="8">
-        <v>32.292091525423729</v>
+        <v>34.011811258278144</v>
       </c>
       <c r="Y97" s="6">
-        <v>0.7024793388429752</v>
+        <v>0.67532467532467533</v>
       </c>
       <c r="Z97" s="6">
-        <v>0.16101694915254236</v>
+        <v>0.2185430463576159</v>
       </c>
       <c r="AA97" s="8">
-        <v>4.1761908163265309</v>
+        <v>4.6620221311475412</v>
       </c>
       <c r="AB97" s="8">
-        <v>9.8527783333333332</v>
+        <v>11.055229411764707</v>
       </c>
       <c r="AC97" s="8">
-        <v>11.242601000000001</v>
+        <v>13.956465</v>
       </c>
       <c r="AD97" s="8">
-        <v>21.76997272727273</v>
+        <v>23.358766233766232</v>
       </c>
       <c r="AE97" s="6">
-        <v>0.4152542372881356</v>
+        <v>0.35099337748344372</v>
       </c>
       <c r="AF97" s="9"/>
       <c r="AG97" s="5">
-        <v>-458.30000000000001</v>
+        <v>-544.89999999999998</v>
       </c>
       <c r="AH97" s="10">
         <v>1</v>
@@ -13673,7 +13673,7 @@
         <v>3.8591675000000003</v>
       </c>
       <c r="AC98" s="8">
-        <v>9.1769230000000004</v>
+        <v>9.6893239999999992</v>
       </c>
       <c r="AD98" s="8">
         <v>15.696314423076924</v>
@@ -13804,7 +13804,7 @@
         <v>5.0205487577639749</v>
       </c>
       <c r="AC99" s="8">
-        <v>8.806953</v>
+        <v>8.7681810000000002</v>
       </c>
       <c r="AD99" s="8">
         <v>15.617384615384614</v>
@@ -13935,7 +13935,7 @@
         <v>5.6217325991189426</v>
       </c>
       <c r="AC100" s="8">
-        <v>8.7349250000000005</v>
+        <v>8.41934</v>
       </c>
       <c r="AD100" s="8">
         <v>16.260507391304348</v>
@@ -14066,7 +14066,7 @@
         <v>13.58820224719101</v>
       </c>
       <c r="AC101" s="8">
-        <v>18.303470000000001</v>
+        <v>20.221698</v>
       </c>
       <c r="AD101" s="8">
         <v>28.382022471910112</v>
@@ -14197,7 +14197,7 @@
         <v>15.099142765273314</v>
       </c>
       <c r="AC102" s="8">
-        <v>20.866081999999999</v>
+        <v>19.604187</v>
       </c>
       <c r="AD102" s="8">
         <v>27.058986833855801</v>
@@ -14328,7 +14328,7 @@
         <v>13.632974731182795</v>
       </c>
       <c r="AC103" s="8">
-        <v>19.244212999999998</v>
+        <v>18.555517999999999</v>
       </c>
       <c r="AD103" s="8">
         <v>24.247249499999999</v>
@@ -14459,7 +14459,7 @@
         <v>7.2418393103448278</v>
       </c>
       <c r="AC104" s="8">
-        <v>13.664622</v>
+        <v>14.995372</v>
       </c>
       <c r="AD104" s="8">
         <v>24.684910135135134</v>
@@ -14590,7 +14590,7 @@
         <v>11.071062637362637</v>
       </c>
       <c r="AC105" s="8">
-        <v>20.603491999999999</v>
+        <v>20.56522</v>
       </c>
       <c r="AD105" s="8">
         <v>27.657692307692308</v>
@@ -14721,7 +14721,7 @@
         <v>18.298575879396985</v>
       </c>
       <c r="AC106" s="8">
-        <v>27.136161000000001</v>
+        <v>25.092210000000001</v>
       </c>
       <c r="AD106" s="8">
         <v>32.003350753768842</v>
@@ -14852,7 +14852,7 @@
         <v>9.2160974358974368</v>
       </c>
       <c r="AC107" s="8">
-        <v>10.599712999999999</v>
+        <v>12.141546</v>
       </c>
       <c r="AD107" s="8">
         <v>16.699054609929078</v>
@@ -14981,7 +14981,7 @@
         <v>15.382597058823528</v>
       </c>
       <c r="AC108" s="8">
-        <v>25.753359</v>
+        <v>28.204502000000002</v>
       </c>
       <c r="AD108" s="8">
         <v>34.645951428571429</v>
@@ -15112,7 +15112,7 @@
         <v>13.200394605263158</v>
       </c>
       <c r="AC109" s="8">
-        <v>19.431761000000002</v>
+        <v>22.082844000000001</v>
       </c>
       <c r="AD109" s="8">
         <v>27.307013054499365</v>
@@ -15243,7 +15243,7 @@
         <v>10.356441104294477</v>
       </c>
       <c r="AC110" s="8">
-        <v>16.789391999999999</v>
+        <v>17.355523999999999</v>
       </c>
       <c r="AD110" s="8">
         <v>22.156471276595742</v>
@@ -15374,7 +15374,7 @@
         <v>26.966359259259256</v>
       </c>
       <c r="AC111" s="8">
-        <v>33.142076000000003</v>
+        <v>43.663871999999998</v>
       </c>
       <c r="AD111" s="8">
         <v>48.232292857142859</v>
@@ -15505,7 +15505,7 @@
         <v>3.3444448717948716</v>
       </c>
       <c r="AC112" s="8">
-        <v>6.3947539999999998</v>
+        <v>6.5644790000000004</v>
       </c>
       <c r="AD112" s="8">
         <v>12.950000000000001</v>
@@ -15557,7 +15557,7 @@
         <v>19785</v>
       </c>
       <c r="B113" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C113" s="4">
         <v>44</v>
@@ -15594,59 +15594,59 @@
         <v>52</v>
       </c>
       <c r="O113" s="5">
-        <v>22218.32</v>
+        <v>30560.720000000001</v>
       </c>
       <c r="P113" s="5">
-        <v>22218.32</v>
+        <v>30560.720000000001</v>
       </c>
       <c r="Q113" s="6">
-        <v>-0.20566672017440901</v>
+        <v>-0.16833906583491642</v>
       </c>
       <c r="R113" s="7">
-        <v>209</v>
+        <v>286</v>
       </c>
       <c r="S113" s="6">
-        <v>-0.25357142857142856</v>
+        <v>-0.2142857142857143</v>
       </c>
       <c r="T113" s="6">
-        <v>0.26143026565464894</v>
+        <v>0.26172688012586087</v>
       </c>
       <c r="U113" s="6">
-        <v>-0.012621057757742259</v>
+        <v>-0.011248036695470526</v>
       </c>
       <c r="V113" s="6">
-        <v>0.013059493247014177</v>
+        <v>0.012533098042192724</v>
       </c>
       <c r="W113" s="6">
-        <v>-0.0077490107262835348</v>
+        <v>-0.006056450895135978</v>
       </c>
       <c r="X113" s="8">
-        <v>24.698658620689656</v>
+        <v>25.394257142857143</v>
       </c>
       <c r="Y113" s="6">
-        <v>0.5977011494252874</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Z113" s="6">
-        <v>0.080459770114942528</v>
+        <v>0.067226890756302518</v>
       </c>
       <c r="AA113" s="8">
-        <v>5.9586956521739136</v>
+        <v>6.0458187279151945</v>
       </c>
       <c r="AB113" s="8">
-        <v>6.5660341772151893</v>
+        <v>7.3280373831775707</v>
       </c>
       <c r="AC113" s="8">
         <v>12.17178</v>
       </c>
       <c r="AD113" s="8">
-        <v>18.217433333333332</v>
+        <v>18.886835294117645</v>
       </c>
       <c r="AE113" s="6">
-        <v>0.74712643678160917</v>
+        <v>0.78151260504201681</v>
       </c>
       <c r="AF113" s="9"/>
       <c r="AG113" s="5">
-        <v>-1377.9000000000001</v>
+        <v>-2184</v>
       </c>
       <c r="AH113" s="10">
         <v>4</v>
@@ -15765,7 +15765,7 @@
         <v>8.9010556962025316</v>
       </c>
       <c r="AC114" s="8">
-        <v>19.438396999999998</v>
+        <v>16.945239999999998</v>
       </c>
       <c r="AD114" s="8">
         <v>23.717931645569621</v>
@@ -15894,7 +15894,7 @@
         <v>8.9560346264367805</v>
       </c>
       <c r="AC115" s="8">
-        <v>24.489450000000001</v>
+        <v>20.665963999999999</v>
       </c>
       <c r="AD115" s="8">
         <v>26.615000000000002</v>
@@ -16025,7 +16025,7 @@
         <v>4.1351554621848745</v>
       </c>
       <c r="AC116" s="8">
-        <v>9.3140859999999996</v>
+        <v>9.3695489999999992</v>
       </c>
       <c r="AD116" s="8">
         <v>11.399132947976879</v>
@@ -16376,7 +16376,7 @@
         <v>10.414985994397759</v>
       </c>
       <c r="AC119" s="8">
-        <v>16.028025</v>
+        <v>16.885375</v>
       </c>
       <c r="AD119" s="8">
         <v>24.348513513513517</v>
@@ -16507,7 +16507,7 @@
         <v>2.4414029411764711</v>
       </c>
       <c r="AC120" s="8">
-        <v>4.7614679999999998</v>
+        <v>5.7867449999999998</v>
       </c>
       <c r="AD120" s="8">
         <v>12.502734589800443</v>
@@ -16638,7 +16638,7 @@
         <v>19.449727247956403</v>
       </c>
       <c r="AC121" s="8">
-        <v>26.4011</v>
+        <v>25.334800999999999</v>
       </c>
       <c r="AD121" s="8">
         <v>32.809822400000002</v>
@@ -16769,7 +16769,7 @@
         <v>13.506837435897435</v>
       </c>
       <c r="AC122" s="8">
-        <v>24.720227999999999</v>
+        <v>22.190531</v>
       </c>
       <c r="AD122" s="8">
         <v>27.851674641148325</v>
@@ -16898,7 +16898,7 @@
         <v>2.8521815436241611</v>
       </c>
       <c r="AC123" s="8">
-        <v>8.7173599999999993</v>
+        <v>8.6112269999999995</v>
       </c>
       <c r="AD123" s="8">
         <v>15.458168421052632</v>
@@ -17047,7 +17047,7 @@
         <v>19842</v>
       </c>
       <c r="B125" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C125" s="4">
         <v>44</v>
@@ -17084,59 +17084,59 @@
         <v>52</v>
       </c>
       <c r="O125" s="5">
-        <v>53927.970000000008</v>
+        <v>67539.160000000003</v>
       </c>
       <c r="P125" s="5">
-        <v>53927.970000000008</v>
+        <v>67539.160000000003</v>
       </c>
       <c r="Q125" s="6">
-        <v>-0.084575941383494779</v>
+        <v>-0.071700037454084375</v>
       </c>
       <c r="R125" s="7">
-        <v>524</v>
+        <v>653</v>
       </c>
       <c r="S125" s="6">
-        <v>-0.16693163751987283</v>
+        <v>-0.14973958333333337</v>
       </c>
       <c r="T125" s="6">
-        <v>0.32070073284790807</v>
+        <v>0.31259882266821204</v>
       </c>
       <c r="U125" s="6">
-        <v>0.0040083003309785261</v>
+        <v>-0.0024224183421884429</v>
       </c>
       <c r="V125" s="6">
-        <v>0.022624011250562556</v>
+        <v>0.022773165967714136</v>
       </c>
       <c r="W125" s="6">
-        <v>0.0077146794140406172</v>
+        <v>0.0080781357067514614</v>
       </c>
       <c r="X125" s="8">
-        <v>30.633234421364985</v>
+        <v>32.189411238532109</v>
       </c>
       <c r="Y125" s="6">
-        <v>0.88130563798219586</v>
+        <v>0.85779816513761464</v>
       </c>
       <c r="Z125" s="6">
-        <v>0.10385756676557864</v>
+        <v>0.19036697247706422</v>
       </c>
       <c r="AA125" s="8">
-        <v>5.3954909819639276</v>
+        <v>5.7604299363057327</v>
       </c>
       <c r="AB125" s="8">
-        <v>10.813931578947368</v>
+        <v>12.241972127139364</v>
       </c>
       <c r="AC125" s="8">
         <v>16.211711999999999</v>
       </c>
       <c r="AD125" s="8">
-        <v>23.233283976261127</v>
+        <v>24.526873165137616</v>
       </c>
       <c r="AE125" s="6">
-        <v>0.48071216617210683</v>
+        <v>0.41055045871559631</v>
       </c>
       <c r="AF125" s="9"/>
       <c r="AG125" s="5">
-        <v>-11786.370000000001</v>
+        <v>-14309.57</v>
       </c>
       <c r="AH125" s="10">
         <v>3</v>
@@ -17436,7 +17436,7 @@
         <v>19859</v>
       </c>
       <c r="B128" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C128" s="4">
         <v>44</v>
@@ -17473,55 +17473,55 @@
         <v>52</v>
       </c>
       <c r="O128" s="5">
-        <v>23495.799999999999</v>
+        <v>29937.16</v>
       </c>
       <c r="P128" s="5">
-        <v>23495.799999999999</v>
+        <v>29937.16</v>
       </c>
       <c r="Q128" s="6">
-        <v>-0.337463786628588</v>
+        <v>-0.29868433443889653</v>
       </c>
       <c r="R128" s="7">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="S128" s="6">
-        <v>-0.33514986376021794</v>
+        <v>-0.29680365296803657</v>
       </c>
       <c r="T128" s="6">
-        <v>0.31397113526672854</v>
+        <v>0.31298146183539116</v>
       </c>
       <c r="U128" s="6">
-        <v>-0.0064814562602677926</v>
+        <v>-0.0091603178123776611</v>
       </c>
       <c r="V128" s="6">
-        <v>0.027456524144740764</v>
+        <v>0.026105916526484144</v>
       </c>
       <c r="W128" s="6">
-        <v>-0.0019048936405655478</v>
+        <v>-0.001635191848525378</v>
       </c>
       <c r="X128" s="8">
-        <v>33.230584020618558</v>
+        <v>34.144173170731705</v>
       </c>
       <c r="Y128" s="6">
-        <v>0.54639175257731953</v>
+        <v>0.47967479674796748</v>
       </c>
       <c r="Z128" s="6">
-        <v>0.25773195876288657</v>
+        <v>0.2886178861788618</v>
       </c>
       <c r="AA128" s="8">
-        <v>7.7475510204081637</v>
+        <v>8.5786407766990305</v>
       </c>
       <c r="AB128" s="8">
-        <v>6.6647762886597937</v>
+        <v>6.8448508130081303</v>
       </c>
       <c r="AC128" s="8">
         <v>14.925718</v>
       </c>
       <c r="AD128" s="8">
-        <v>21.834020103092783</v>
+        <v>22.90304837398374</v>
       </c>
       <c r="AE128" s="6">
-        <v>0.4845360824742268</v>
+        <v>0.42682926829268292</v>
       </c>
       <c r="AF128" s="9"/>
       <c r="AG128" s="5">
@@ -17737,7 +17737,7 @@
         <v>6.7704823293172698</v>
       </c>
       <c r="AC130" s="8">
-        <v>15.597854999999999</v>
+        <v>15.257239</v>
       </c>
       <c r="AD130" s="8">
         <v>22.10929641434263</v>
@@ -17993,7 +17993,7 @@
         <v>21.982803703703702</v>
       </c>
       <c r="AC132" s="8">
-        <v>12.476850000000001</v>
+        <v>35.446568999999997</v>
       </c>
       <c r="AD132" s="8">
         <v>42.776822916666667</v>
@@ -18124,7 +18124,7 @@
         <v>10.81487415730337</v>
       </c>
       <c r="AC133" s="8">
-        <v>16.310365000000001</v>
+        <v>16.100701999999998</v>
       </c>
       <c r="AD133" s="8">
         <v>22.303263946587538</v>
@@ -18255,7 +18255,7 @@
         <v>18.500980147058822</v>
       </c>
       <c r="AC134" s="8">
-        <v>18.154875000000001</v>
+        <v>28.302864</v>
       </c>
       <c r="AD134" s="8">
         <v>34.725239568345323</v>
@@ -18386,7 +18386,7 @@
         <v>18.902472903225807</v>
       </c>
       <c r="AC135" s="8">
-        <v>18.794557999999999</v>
+        <v>22.85981</v>
       </c>
       <c r="AD135" s="8">
         <v>29.324894303797471</v>
@@ -18438,7 +18438,7 @@
         <v>19881</v>
       </c>
       <c r="B136" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C136" s="4">
         <v>44</v>
@@ -18475,55 +18475,55 @@
         <v>52</v>
       </c>
       <c r="O136" s="5">
-        <v>61251.619999999995</v>
+        <v>77036.239999999991</v>
       </c>
       <c r="P136" s="5">
-        <v>61251.619999999995</v>
+        <v>77036.239999999991</v>
       </c>
       <c r="Q136" s="6">
-        <v>0.038035143805161598</v>
+        <v>0.040477832783107459</v>
       </c>
       <c r="R136" s="7">
-        <v>541</v>
+        <v>681</v>
       </c>
       <c r="S136" s="6">
-        <v>0.013108614232209659</v>
+        <v>-0.005839416058394109</v>
       </c>
       <c r="T136" s="6">
-        <v>0.29605034446435863</v>
+        <v>0.48065112601549609</v>
       </c>
       <c r="U136" s="6">
-        <v>-0.04011627447567917</v>
+        <v>0.15069551032085676</v>
       </c>
       <c r="V136" s="6">
-        <v>0.021977181991268146</v>
+        <v>0.022773878891285449</v>
       </c>
       <c r="W136" s="6">
-        <v>4.6823251368698489E-05</v>
+        <v>0.00071542951732846767</v>
       </c>
       <c r="X136" s="8">
-        <v>29.390091293532336</v>
+        <v>28.661990781563127</v>
       </c>
       <c r="Y136" s="6">
-        <v>0.65174129353233834</v>
+        <v>0.63927855711422843</v>
       </c>
       <c r="Z136" s="6">
-        <v>0.16417910447761194</v>
+        <v>0.13426853707414829</v>
       </c>
       <c r="AA136" s="8">
-        <v>3.2238355716878404</v>
+        <v>3.2621147398843933</v>
       </c>
       <c r="AB136" s="8">
-        <v>11.91222205128205</v>
+        <v>11.123887679671459</v>
       </c>
       <c r="AC136" s="8">
         <v>15.11074</v>
       </c>
       <c r="AD136" s="8">
-        <v>20.931467910447761</v>
+        <v>20.250902004008015</v>
       </c>
       <c r="AE136" s="6">
-        <v>0.62189054726368154</v>
+        <v>0.64729458917835669</v>
       </c>
       <c r="AF136" s="9"/>
       <c r="AG136" s="5">
@@ -18648,7 +18648,7 @@
         <v>5.4116461847389559</v>
       </c>
       <c r="AC137" s="8">
-        <v>8.2062570000000008</v>
+        <v>9.2815940000000001</v>
       </c>
       <c r="AD137" s="8">
         <v>15.862274418604652</v>
@@ -18700,7 +18700,7 @@
         <v>19884</v>
       </c>
       <c r="B138" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C138" s="4">
         <v>44</v>
@@ -18737,55 +18737,55 @@
         <v>52</v>
       </c>
       <c r="O138" s="5">
-        <v>21610.779999999999</v>
+        <v>27885.639999999999</v>
       </c>
       <c r="P138" s="5">
-        <v>21610.779999999999</v>
+        <v>27885.639999999999</v>
       </c>
       <c r="Q138" s="6">
-        <v>-0.30767121304055611</v>
+        <v>-0.28861602575974876</v>
       </c>
       <c r="R138" s="7">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="S138" s="6">
-        <v>-0.29080118694362023</v>
+        <v>-0.26987951807228916</v>
       </c>
       <c r="T138" s="6">
-        <v>0.33164228223136788</v>
+        <v>0.325168559875262</v>
       </c>
       <c r="U138" s="6">
-        <v>0.0051108011834834289</v>
+        <v>0.0050568464629106588</v>
       </c>
       <c r="V138" s="6">
-        <v>0.025575152770978188</v>
+        <v>0.026683733993553671</v>
       </c>
       <c r="W138" s="6">
-        <v>-0.026535414270100387</v>
+        <v>-0.022595034576936374</v>
       </c>
       <c r="X138" s="8">
-        <v>33.448546511627903</v>
+        <v>34.676308071748878</v>
       </c>
       <c r="Y138" s="6">
-        <v>0.48255813953488375</v>
+        <v>0.40358744394618834</v>
       </c>
       <c r="Z138" s="6">
-        <v>0.21511627906976744</v>
+        <v>0.27802690582959644</v>
       </c>
       <c r="AA138" s="8">
-        <v>8.5979508196721319</v>
+        <v>8.3065477272727275</v>
       </c>
       <c r="AB138" s="8">
-        <v>7.2729166666666663</v>
+        <v>7.9418848167539275</v>
       </c>
       <c r="AC138" s="8">
         <v>17.417134999999998</v>
       </c>
       <c r="AD138" s="8">
-        <v>22.550097093023258</v>
+        <v>22.694618834080718</v>
       </c>
       <c r="AE138" s="6">
-        <v>0.38953488372093026</v>
+        <v>0.33183856502242154</v>
       </c>
       <c r="AF138" s="9"/>
       <c r="AG138" s="5">
@@ -18910,7 +18910,7 @@
         <v>3.3077433070866142</v>
       </c>
       <c r="AC139" s="8">
-        <v>9.331664</v>
+        <v>10.193142999999999</v>
       </c>
       <c r="AD139" s="8">
         <v>16.556227106227109</v>
@@ -19041,7 +19041,7 @@
         <v>3.9173860911270983</v>
       </c>
       <c r="AC140" s="8">
-        <v>7.5530119999999998</v>
+        <v>8.698283</v>
       </c>
       <c r="AD140" s="8">
         <v>15.490848831775702</v>
@@ -19172,7 +19172,7 @@
         <v>4.2345238095238091</v>
       </c>
       <c r="AC141" s="8">
-        <v>15.515184</v>
+        <v>16.349807999999999</v>
       </c>
       <c r="AD141" s="8">
         <v>23.275049112426036</v>
@@ -19301,7 +19301,7 @@
         <v>11.640339490445861</v>
       </c>
       <c r="AC142" s="8">
-        <v>16.488537000000001</v>
+        <v>17.406172000000002</v>
       </c>
       <c r="AD142" s="8">
         <v>24.272257594936711</v>
@@ -19432,7 +19432,7 @@
         <v>1.642019014084507</v>
       </c>
       <c r="AC143" s="8">
-        <v>5.1017460000000003</v>
+        <v>5.127332</v>
       </c>
       <c r="AD143" s="8">
         <v>12.05641048951049</v>
@@ -19563,7 +19563,7 @@
         <v>2.5951934883720931</v>
       </c>
       <c r="AC144" s="8">
-        <v>5.8776849999999996</v>
+        <v>6.4977510000000001</v>
       </c>
       <c r="AD144" s="8">
         <v>13.445968837209302</v>
@@ -19837,7 +19837,7 @@
         <v>19910</v>
       </c>
       <c r="B147" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C147" s="4">
         <v>44</v>
@@ -19874,55 +19874,55 @@
         <v>52</v>
       </c>
       <c r="O147" s="5">
-        <v>19128.139999999999</v>
+        <v>25473.889999999999</v>
       </c>
       <c r="P147" s="5">
-        <v>19128.139999999999</v>
+        <v>25473.889999999999</v>
       </c>
       <c r="Q147" s="6">
-        <v>0.18243398619761986</v>
+        <v>0.11987319713440647</v>
       </c>
       <c r="R147" s="7">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="S147" s="6">
-        <v>0.23163841807909602</v>
+        <v>0.12000000000000011</v>
       </c>
       <c r="T147" s="6">
-        <v>0.91587341999797167</v>
+        <v>0.6805114962810942</v>
       </c>
       <c r="U147" s="6">
-        <v>0.61092740851959471</v>
+        <v>0.3722864862806583</v>
       </c>
       <c r="V147" s="6">
-        <v>0.070439885948137146</v>
+        <v>0.075151655283115376</v>
       </c>
       <c r="W147" s="6">
-        <v>0.039379364642876939</v>
+        <v>0.047197149708976531</v>
       </c>
       <c r="X147" s="8">
-        <v>23.52076557377049</v>
+        <v>21.506837820512821</v>
       </c>
       <c r="Y147" s="6">
-        <v>0.86885245901639341</v>
+        <v>0.88461538461538458</v>
       </c>
       <c r="Z147" s="6">
-        <v>0.049180327868852458</v>
+        <v>0.038461538461538464</v>
       </c>
       <c r="AA147" s="8">
-        <v>5.638162149532711</v>
+        <v>5.1200485507246372</v>
       </c>
       <c r="AB147" s="8">
-        <v>11.236857692307693</v>
+        <v>9.7521852459016394</v>
       </c>
       <c r="AC147" s="8">
         <v>17.195601</v>
       </c>
       <c r="AD147" s="8">
-        <v>17.107300826446281</v>
+        <v>15.534839354838709</v>
       </c>
       <c r="AE147" s="6">
-        <v>0.89344262295081966</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="AF147" s="9"/>
       <c r="AG147" s="5">
@@ -20047,7 +20047,7 @@
         <v>5.0561332000000005</v>
       </c>
       <c r="AC148" s="8">
-        <v>10.365188</v>
+        <v>10.230109000000001</v>
       </c>
       <c r="AD148" s="8">
         <v>16.205487692307692</v>
@@ -20309,7 +20309,7 @@
         <v>14.10692533783784</v>
       </c>
       <c r="AC150" s="8">
-        <v>21.816662999999998</v>
+        <v>21.625086</v>
       </c>
       <c r="AD150" s="8">
         <v>29.118333124999999</v>
@@ -20533,7 +20533,7 @@
         <v>8.5630443478260876</v>
       </c>
       <c r="AC152" s="8">
-        <v>18.568062999999999</v>
+        <v>18.229575000000001</v>
       </c>
       <c r="AD152" s="8">
         <v>24.716804132231402</v>
@@ -20585,7 +20585,7 @@
         <v>19927</v>
       </c>
       <c r="B153" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C153" s="4">
         <v>44</v>
@@ -20622,55 +20622,55 @@
         <v>52</v>
       </c>
       <c r="O153" s="5">
-        <v>8726.6599999999999</v>
+        <v>10822.639999999999</v>
       </c>
       <c r="P153" s="5">
-        <v>8726.6599999999999</v>
+        <v>10822.639999999999</v>
       </c>
       <c r="Q153" s="6">
-        <v>-0.11064707099304238</v>
+        <v>-0.10186529107984721</v>
       </c>
       <c r="R153" s="7">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="S153" s="6">
-        <v>-0.098360655737704916</v>
+        <v>-0.09210526315789469</v>
       </c>
       <c r="T153" s="6">
-        <v>0</v>
+        <v>0.0041708862163021224</v>
       </c>
       <c r="U153" s="6">
-        <v>-0.32542232652584152</v>
+        <v>-0.3199681408602707</v>
       </c>
       <c r="V153" s="6">
-        <v>0.12414337214925297</v>
+        <v>0.12185441814566501</v>
       </c>
       <c r="W153" s="6">
-        <v>0.047427881915876179</v>
+        <v>0.048309515977617297</v>
       </c>
       <c r="X153" s="8">
-        <v>41.633333333333333</v>
+        <v>38.619230769230768</v>
       </c>
       <c r="Y153" s="6">
-        <v>0.45454545454545453</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="Z153" s="6">
-        <v>0.42424242424242425</v>
+        <v>0.31868131868131866</v>
       </c>
       <c r="AA153" s="8">
-        <v>9.6891891891891895</v>
+        <v>9.1664266187050352</v>
       </c>
       <c r="AB153" s="8">
-        <v>13.117928787878789</v>
+        <v>11.812222222222221</v>
       </c>
       <c r="AC153" s="8">
-        <v>19.709374</v>
+        <v>22.161957999999998</v>
       </c>
       <c r="AD153" s="8">
-        <v>29.206816666666665</v>
+        <v>27.089009890109892</v>
       </c>
       <c r="AE153" s="6">
-        <v>0.25757575757575757</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="AF153" s="9"/>
       <c r="AG153" s="5">
@@ -20797,7 +20797,7 @@
         <v>11.106737588652482</v>
       </c>
       <c r="AC154" s="8">
-        <v>17.263026</v>
+        <v>16.167660000000001</v>
       </c>
       <c r="AD154" s="8">
         <v>22.527231864406779</v>
@@ -20849,7 +20849,7 @@
         <v>19930</v>
       </c>
       <c r="B155" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C155" s="4">
         <v>44</v>
@@ -20886,59 +20886,59 @@
         <v>52</v>
       </c>
       <c r="O155" s="5">
-        <v>21979.389999999999</v>
+        <v>29465.239999999998</v>
       </c>
       <c r="P155" s="5">
-        <v>21979.389999999999</v>
+        <v>29465.239999999998</v>
       </c>
       <c r="Q155" s="6">
-        <v>0.14529615689846431</v>
+        <v>0.13382705940027884</v>
       </c>
       <c r="R155" s="7">
-        <v>325</v>
+        <v>442</v>
       </c>
       <c r="S155" s="6">
-        <v>0.11301369863013688</v>
+        <v>0.096774193548387011</v>
       </c>
       <c r="T155" s="6">
-        <v>0.36777986559226622</v>
+        <v>0.3613568971438888</v>
       </c>
       <c r="U155" s="6">
-        <v>0.030969335363720287</v>
+        <v>0.024595004147259618</v>
       </c>
       <c r="V155" s="6">
-        <v>0.070500864673678387</v>
+        <v>0.066748616335723029</v>
       </c>
       <c r="W155" s="6">
-        <v>0.036035394976839663</v>
+        <v>0.034773991319941737</v>
       </c>
       <c r="X155" s="8">
-        <v>28.103101824817518</v>
+        <v>28.211110852713176</v>
       </c>
       <c r="Y155" s="6">
-        <v>0.14233576642335766</v>
+        <v>0.12403100775193798</v>
       </c>
       <c r="Z155" s="6">
-        <v>0.12408759124087591</v>
+        <v>0.10077519379844961</v>
       </c>
       <c r="AA155" s="8">
-        <v>4.7077199386503068</v>
+        <v>4.692851918735891</v>
       </c>
       <c r="AB155" s="8">
-        <v>11.687856505576207</v>
+        <v>11.426290551181102</v>
       </c>
       <c r="AC155" s="8">
-        <v>16.129113</v>
+        <v>16.461492</v>
       </c>
       <c r="AD155" s="8">
-        <v>23.090571532846717</v>
+        <v>22.819121188630493</v>
       </c>
       <c r="AE155" s="6">
-        <v>0.66058394160583944</v>
+        <v>0.65633074935400515</v>
       </c>
       <c r="AF155" s="9"/>
       <c r="AG155" s="5">
-        <v>-142.80000000000001</v>
+        <v>-288.39999999999998</v>
       </c>
       <c r="AH155" s="10">
         <v>3</v>
@@ -20980,7 +20980,7 @@
         <v>19931</v>
       </c>
       <c r="B156" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C156" s="4">
         <v>44</v>
@@ -21017,59 +21017,59 @@
         <v>52</v>
       </c>
       <c r="O156" s="5">
-        <v>24728.470000000001</v>
+        <v>35963.740000000005</v>
       </c>
       <c r="P156" s="5">
-        <v>24728.470000000001</v>
+        <v>35963.740000000005</v>
       </c>
       <c r="Q156" s="6">
-        <v>0.035198941712558662</v>
+        <v>0.086085031372694854</v>
       </c>
       <c r="R156" s="7">
-        <v>258</v>
+        <v>377</v>
       </c>
       <c r="S156" s="6">
-        <v>-0.12244897959183676</v>
+        <v>-0.075980392156862697</v>
       </c>
       <c r="T156" s="6">
-        <v>0.30477841936844452</v>
+        <v>0.31993692535870855</v>
       </c>
       <c r="U156" s="6">
-        <v>-0.17324711152772493</v>
+        <v>-0.15666867795173695</v>
       </c>
       <c r="V156" s="6">
-        <v>0.059086672163704425</v>
+        <v>0.055593786964314613</v>
       </c>
       <c r="W156" s="6">
-        <v>0.034857918827974392</v>
+        <v>0.035309189200010901</v>
       </c>
       <c r="X156" s="8">
-        <v>25.848470642201832</v>
+        <v>25.227956774193547</v>
       </c>
       <c r="Y156" s="6">
-        <v>0.61467889908256879</v>
+        <v>0.6645161290322581</v>
       </c>
       <c r="Z156" s="6">
-        <v>0.027522935779816515</v>
+        <v>0.01935483870967742</v>
       </c>
       <c r="AA156" s="8">
-        <v>4.7310936758893281</v>
+        <v>4.6928636856368566</v>
       </c>
       <c r="AB156" s="8">
-        <v>4.6699999999999999</v>
+        <v>4.5500000000000007</v>
       </c>
       <c r="AC156" s="8">
-        <v>9.1503029999999992</v>
+        <v>9.7110599999999998</v>
       </c>
       <c r="AD156" s="8">
-        <v>16.373393577981652</v>
+        <v>16.182687741935485</v>
       </c>
       <c r="AE156" s="6">
-        <v>0.73394495412844041</v>
+        <v>0.78064516129032258</v>
       </c>
       <c r="AF156" s="9"/>
       <c r="AG156" s="5">
-        <v>-376.5</v>
+        <v>-446.30000000000001</v>
       </c>
       <c r="AH156" s="10">
         <v>2</v>
@@ -21190,7 +21190,7 @@
         <v>5.4461421296296297</v>
       </c>
       <c r="AC157" s="8">
-        <v>9.4666200000000007</v>
+        <v>10.194589000000001</v>
       </c>
       <c r="AD157" s="8">
         <v>14.928002205882352</v>
@@ -21319,7 +21319,7 @@
         <v>9.5339872549019606</v>
       </c>
       <c r="AC158" s="8">
-        <v>11.696972000000001</v>
+        <v>12.457001</v>
       </c>
       <c r="AD158" s="8">
         <v>19.205929807692307</v>
@@ -21448,7 +21448,7 @@
         <v>8.562820279720281</v>
       </c>
       <c r="AC159" s="8">
-        <v>14.405317999999999</v>
+        <v>14.329485999999999</v>
       </c>
       <c r="AD159" s="8">
         <v>19.072646470588236</v>
@@ -21502,7 +21502,7 @@
         <v>19943</v>
       </c>
       <c r="B160" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C160" s="4">
         <v>44</v>
@@ -21539,59 +21539,59 @@
         <v>52</v>
       </c>
       <c r="O160" s="5">
-        <v>14824.26</v>
+        <v>20611.77</v>
       </c>
       <c r="P160" s="5">
-        <v>14824.26</v>
+        <v>20611.77</v>
       </c>
       <c r="Q160" s="6">
-        <v>0.053200468333494122</v>
+        <v>0.043453234933495066</v>
       </c>
       <c r="R160" s="7">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="S160" s="6">
-        <v>-0.17000000000000004</v>
+        <v>-0.17266187050359716</v>
       </c>
       <c r="T160" s="6">
-        <v>0.37038156373404135</v>
+        <v>0.34866711592454214</v>
       </c>
       <c r="U160" s="6">
-        <v>0.025842949327656153</v>
+        <v>0.011231272229410671</v>
       </c>
       <c r="V160" s="6">
-        <v>0.060871571329698747</v>
+        <v>0.068688278590339408</v>
       </c>
       <c r="W160" s="6">
-        <v>0.020238851720085861</v>
+        <v>0.029954584201162735</v>
       </c>
       <c r="X160" s="8">
-        <v>35.028595098039219</v>
+        <v>33.429136296296292</v>
       </c>
       <c r="Y160" s="6">
-        <v>0.59803921568627449</v>
+        <v>0.63703703703703707</v>
       </c>
       <c r="Z160" s="6">
-        <v>0.26470588235294118</v>
+        <v>0.22962962962962963</v>
       </c>
       <c r="AA160" s="8">
-        <v>8.6490734567901235</v>
+        <v>9.3661455357142849</v>
       </c>
       <c r="AB160" s="8">
-        <v>15.161</v>
+        <v>13.373737121212121</v>
       </c>
       <c r="AC160" s="8">
         <v>22.930636</v>
       </c>
       <c r="AD160" s="8">
-        <v>29.436600980392157</v>
+        <v>27.766296296296296</v>
       </c>
       <c r="AE160" s="6">
-        <v>0.53921568627450978</v>
+        <v>0.562962962962963</v>
       </c>
       <c r="AF160" s="9"/>
       <c r="AG160" s="5">
-        <v>-187.19999999999999</v>
+        <v>-374.60000000000002</v>
       </c>
       <c r="AH160" s="10">
         <v>2</v>
@@ -21712,7 +21712,7 @@
         <v>7.1599220735785947</v>
       </c>
       <c r="AC161" s="8">
-        <v>13.9491</v>
+        <v>14.006015</v>
       </c>
       <c r="AD161" s="8">
         <v>20.791333666666667</v>
@@ -21843,7 +21843,7 @@
         <v>8.4055538461538468</v>
       </c>
       <c r="AC162" s="8">
-        <v>20.747119999999999</v>
+        <v>19.273703000000001</v>
       </c>
       <c r="AD162" s="8">
         <v>24.671853333333335</v>
@@ -21974,7 +21974,7 @@
         <v>5.7438028169014084</v>
       </c>
       <c r="AC163" s="8">
-        <v>9.5126869999999997</v>
+        <v>9.0209729999999997</v>
       </c>
       <c r="AD163" s="8">
         <v>14.374371859296483</v>
@@ -22105,7 +22105,7 @@
         <v>6.2650232394366192</v>
       </c>
       <c r="AC164" s="8">
-        <v>19.959038</v>
+        <v>22.533541</v>
       </c>
       <c r="AD164" s="8">
         <v>28.748801960784316</v>
@@ -22157,7 +22157,7 @@
         <v>19951</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22194,59 +22194,59 @@
         <v>52</v>
       </c>
       <c r="O165" s="5">
-        <v>22616.130000000001</v>
+        <v>32516.190000000002</v>
       </c>
       <c r="P165" s="5">
-        <v>22616.130000000001</v>
+        <v>32516.190000000002</v>
       </c>
       <c r="Q165" s="6">
-        <v>-0.26645884850010249</v>
+        <v>-0.22202682886388958</v>
       </c>
       <c r="R165" s="7">
-        <v>228</v>
+        <v>330</v>
       </c>
       <c r="S165" s="6">
-        <v>-0.36842105263157898</v>
+        <v>-0.33062880324543609</v>
       </c>
       <c r="T165" s="6">
-        <v>0.38787686045313674</v>
+        <v>0.37961332493136496</v>
       </c>
       <c r="U165" s="6">
-        <v>0.029123616639982169</v>
+        <v>0.021835860843475205</v>
       </c>
       <c r="V165" s="6">
-        <v>0.030141916410986316</v>
+        <v>0.024301063562489948</v>
       </c>
       <c r="W165" s="6">
-        <v>-0.0027381563512413483</v>
+        <v>-0.0026261379331342324</v>
       </c>
       <c r="X165" s="8">
-        <v>25.419067999999999</v>
+        <v>25.286406703910615</v>
       </c>
       <c r="Y165" s="6">
-        <v>0.46400000000000002</v>
+        <v>0.46927374301675978</v>
       </c>
       <c r="Z165" s="6">
-        <v>0.071999999999999995</v>
+        <v>0.061452513966480445</v>
       </c>
       <c r="AA165" s="8">
-        <v>4.7817777777777781</v>
+        <v>5.4757436923076925</v>
       </c>
       <c r="AB165" s="8">
-        <v>5.1151756097560979</v>
+        <v>4.5796397727272726</v>
       </c>
       <c r="AC165" s="8">
-        <v>10.533039</v>
+        <v>10.177842</v>
       </c>
       <c r="AD165" s="8">
-        <v>16.990666399999999</v>
+        <v>16.947486033519553</v>
       </c>
       <c r="AE165" s="6">
-        <v>0.74399999999999999</v>
+        <v>0.75977653631284914</v>
       </c>
       <c r="AF165" s="9"/>
       <c r="AG165" s="5">
-        <v>-1171.53</v>
+        <v>-1560.76</v>
       </c>
       <c r="AH165" s="10">
         <v>1</v>
@@ -22288,7 +22288,7 @@
         <v>19954</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C166" s="4">
         <v>44</v>
@@ -22325,59 +22325,59 @@
         <v>52</v>
       </c>
       <c r="O166" s="5">
-        <v>8790.8299999999999</v>
+        <v>12766.01</v>
       </c>
       <c r="P166" s="5">
-        <v>8790.8299999999999</v>
+        <v>12766.01</v>
       </c>
       <c r="Q166" s="6">
-        <v>-0.076814586422579323</v>
+        <v>0.00052040186937141186</v>
       </c>
       <c r="R166" s="7">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="S166" s="6">
-        <v>-0.31137724550898205</v>
+        <v>-0.21904761904761905</v>
       </c>
       <c r="T166" s="6">
-        <v>0.4114058171981485</v>
+        <v>0.55087324073849231</v>
       </c>
       <c r="U166" s="6">
-        <v>0.058609778598835378</v>
+        <v>0.18626440837818553</v>
       </c>
       <c r="V166" s="6">
-        <v>0.13190153830753182</v>
+        <v>0.11743735904953857</v>
       </c>
       <c r="W166" s="6">
-        <v>0.068242020378053034</v>
+        <v>0.065118741094515833</v>
       </c>
       <c r="X166" s="8">
-        <v>24.383332352941178</v>
+        <v>25.09781666666667</v>
       </c>
       <c r="Y166" s="6">
-        <v>0.79411764705882348</v>
+        <v>0.80952380952380953</v>
       </c>
       <c r="Z166" s="6">
-        <v>0.029411764705882353</v>
+        <v>0.023809523809523808</v>
       </c>
       <c r="AA166" s="8">
-        <v>5.9636901785714285</v>
+        <v>7.3983434782608697</v>
       </c>
       <c r="AB166" s="8">
-        <v>2.770098529411765</v>
+        <v>2.7087309523809524</v>
       </c>
       <c r="AC166" s="8">
-        <v>8.8715670000000006</v>
+        <v>9.2742640000000005</v>
       </c>
       <c r="AD166" s="8">
-        <v>16.232352941176469</v>
+        <v>16.831746428571428</v>
       </c>
       <c r="AE166" s="6">
-        <v>0.82352941176470584</v>
+        <v>0.79761904761904767</v>
       </c>
       <c r="AF166" s="9"/>
       <c r="AG166" s="5">
-        <v>-291.08999999999997</v>
+        <v>-604.09000000000003</v>
       </c>
       <c r="AH166" s="10">
         <v>3</v>
@@ -22419,7 +22419,7 @@
         <v>19956</v>
       </c>
       <c r="B167" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C167" s="4">
         <v>44</v>
@@ -22456,59 +22456,59 @@
         <v>52</v>
       </c>
       <c r="O167" s="5">
-        <v>7392.2699999999995</v>
+        <v>10140.74</v>
       </c>
       <c r="P167" s="5">
-        <v>7392.2699999999995</v>
+        <v>10140.74</v>
       </c>
       <c r="Q167" s="6">
-        <v>-0.66701966458141149</v>
+        <v>-0.62999790201497774</v>
       </c>
       <c r="R167" s="7">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="S167" s="6">
-        <v>-0.62301587301587302</v>
+        <v>-0.60436137071651097</v>
       </c>
       <c r="T167" s="6">
-        <v>0.34837788663022312</v>
+        <v>0.33937948315408933</v>
       </c>
       <c r="U167" s="6">
-        <v>-0.033623853024848931</v>
+        <v>-0.032631829629790332</v>
       </c>
       <c r="V167" s="6">
-        <v>0.073376987041869415</v>
+        <v>0.075595962424832908</v>
       </c>
       <c r="W167" s="6">
-        <v>0.042243113414418026</v>
+        <v>0.049232008709423576</v>
       </c>
       <c r="X167" s="8">
-        <v>29.065320967741936</v>
+        <v>31.400436842105261</v>
       </c>
       <c r="Y167" s="6">
         <v>0.8571428571428571</v>
       </c>
       <c r="Z167" s="6">
-        <v>0.080645161290322578</v>
+        <v>0.15789473684210525</v>
       </c>
       <c r="AA167" s="8">
-        <v>6.5905225490196075</v>
+        <v>6.7728682170542642</v>
       </c>
       <c r="AB167" s="8">
-        <v>10.066935483870967</v>
+        <v>10.793201315789474</v>
       </c>
       <c r="AC167" s="8">
         <v>16.094213</v>
       </c>
       <c r="AD167" s="8">
-        <v>22.917203225806453</v>
+        <v>23.965350000000001</v>
       </c>
       <c r="AE167" s="6">
-        <v>0.61290322580645162</v>
+        <v>0.5</v>
       </c>
       <c r="AF167" s="9"/>
       <c r="AG167" s="5">
-        <v>-885.97000000000003</v>
+        <v>-2680.2399999999998</v>
       </c>
       <c r="AH167" s="10">
         <v>4</v>
@@ -22602,10 +22602,10 @@
         <v>-0.38414634146341464</v>
       </c>
       <c r="T168" s="6">
-        <v>0.39679493593716508</v>
+        <v>0.39495577217147521</v>
       </c>
       <c r="U168" s="6">
-        <v>0.055301579704940249</v>
+        <v>0.053462415939250364</v>
       </c>
       <c r="V168" s="6">
         <v>0.026979482226328316</v>
@@ -22629,7 +22629,7 @@
         <v>7.2326612903225804</v>
       </c>
       <c r="AC168" s="8">
-        <v>16.825113000000002</v>
+        <v>17.308776000000002</v>
       </c>
       <c r="AD168" s="8">
         <v>24.044799999999999</v>
@@ -22756,7 +22756,7 @@
         <v>3.5865979381443296</v>
       </c>
       <c r="AC169" s="8">
-        <v>9.0604469999999999</v>
+        <v>8.9843089999999997</v>
       </c>
       <c r="AD169" s="8">
         <v>15.921649484536083</v>
@@ -22808,7 +22808,7 @@
         <v>19961</v>
       </c>
       <c r="B170" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C170" s="4">
         <v>44</v>
@@ -22845,55 +22845,55 @@
         <v>52</v>
       </c>
       <c r="O170" s="5">
-        <v>17046.330000000002</v>
+        <v>20939.880000000001</v>
       </c>
       <c r="P170" s="5">
-        <v>17046.330000000002</v>
+        <v>20939.880000000001</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="7">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="S170" s="6"/>
       <c r="T170" s="6">
-        <v>0.32673818939325938</v>
+        <v>0.33770461435309085</v>
       </c>
       <c r="U170" s="6">
-        <v>-0.028882639254314564</v>
+        <v>-0.016237719604887898</v>
       </c>
       <c r="V170" s="6">
-        <v>0.033263523585428646</v>
+        <v>0.033154201456741868</v>
       </c>
       <c r="W170" s="6">
-        <v>0.017234853484591695</v>
+        <v>0.017496518604691143</v>
       </c>
       <c r="X170" s="8">
-        <v>39.125601030927839</v>
+        <v>37.421250000000001</v>
       </c>
       <c r="Y170" s="6">
-        <v>0.32989690721649484</v>
+        <v>0.375</v>
       </c>
       <c r="Z170" s="6">
-        <v>0.36082474226804123</v>
+        <v>0.30833333333333335</v>
       </c>
       <c r="AA170" s="8">
-        <v>7.602986705202313</v>
+        <v>7.2743712264150941</v>
       </c>
       <c r="AB170" s="8">
-        <v>11.005730208333333</v>
+        <v>10.138515966386555</v>
       </c>
       <c r="AC170" s="8">
-        <v>12.86111</v>
+        <v>19.06785</v>
       </c>
       <c r="AD170" s="8">
-        <v>25.830755670103091</v>
+        <v>24.519166666666667</v>
       </c>
       <c r="AE170" s="6">
-        <v>0.38144329896907214</v>
+        <v>0.40833333333333333</v>
       </c>
       <c r="AF170" s="9"/>
       <c r="AG170" s="5">
-        <v>-805.5</v>
+        <v>-1143.5</v>
       </c>
       <c r="AH170" s="10">
         <v>2</v>
@@ -23137,7 +23137,7 @@
         <v>6.9694317535545016</v>
       </c>
       <c r="AC172" s="8">
-        <v>19.659884000000002</v>
+        <v>18.696066999999999</v>
       </c>
       <c r="AD172" s="8">
         <v>25.63169061032864</v>
@@ -23355,7 +23355,7 @@
         <v>6.6814104395604392</v>
       </c>
       <c r="AC174" s="8">
-        <v>10.942467000000001</v>
+        <v>13.684618</v>
       </c>
       <c r="AD174" s="8">
         <v>20.324688235294118</v>
